--- a/data/IKPA_SEPTEMBER_2025.xlsx
+++ b/data/IKPA_SEPTEMBER_2025.xlsx
@@ -632,7 +632,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -641,17 +641,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -711,13 +711,13 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA (403409)</t>
+          <t>RUTAN KELAS II B BATURAJA (692339)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -726,17 +726,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -758,10 +758,10 @@
         <v>100</v>
       </c>
       <c r="L4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
@@ -770,11 +770,11 @@
         <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -796,13 +796,13 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA (401945)</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA (527975)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -811,17 +811,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>440507</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -843,10 +843,10 @@
         <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
@@ -855,11 +855,11 @@
         <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -881,13 +881,13 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA (692339)</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440507)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -896,17 +896,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>402268</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -966,13 +966,13 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA (402268)</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU (428258)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -981,17 +981,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1051,13 +1051,13 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA (402267)</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA (410574)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1066,17 +1066,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>403409</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1136,13 +1136,13 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA (410574)</t>
+          <t>PENGADILAN AGAMA MARTAPURA (403409)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>402268</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1221,13 +1221,13 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU (428258)</t>
+          <t>PENGADILAN AGAMA BATURAJA (402268)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1236,17 +1236,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>440507</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1268,10 +1268,10 @@
         <v>100</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N10" t="n">
         <v>100</v>
@@ -1280,11 +1280,11 @@
         <v>100</v>
       </c>
       <c r="P10" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R10" t="n">
@@ -1306,13 +1306,13 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440507)</t>
+          <t>PENGADILAN AGAMA BATURAJA (402267)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1321,17 +1321,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1353,10 +1353,10 @@
         <v>100</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N11" t="n">
         <v>100</v>
@@ -1365,11 +1365,11 @@
         <v>100</v>
       </c>
       <c r="P11" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R11" t="n">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA (527975)</t>
+          <t>PENGADILAN AGAMA MUARADUA (401945)</t>
         </is>
       </c>
     </row>
@@ -4797,7 +4797,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -4806,55 +4806,55 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>87.17</v>
+        <v>88.88</v>
       </c>
       <c r="G52" t="n">
-        <v>98.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="H52" t="n">
-        <v>100</v>
+        <v>90.56</v>
       </c>
       <c r="I52" t="n">
         <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>74.33</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>96.47</v>
+        <v>100</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N52" t="n">
         <v>100</v>
       </c>
       <c r="O52" t="n">
-        <v>100</v>
+        <v>90.56</v>
       </c>
       <c r="P52" t="n">
-        <v>75.44</v>
+        <v>94.3</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R52" t="n">
@@ -4876,13 +4876,13 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666503)</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN (007208)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -4891,55 +4891,55 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>88.88</v>
+        <v>87.17</v>
       </c>
       <c r="G53" t="n">
-        <v>100</v>
+        <v>98.23999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>90.56</v>
+        <v>100</v>
       </c>
       <c r="I53" t="n">
         <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>77.76000000000001</v>
+        <v>74.33</v>
       </c>
       <c r="K53" t="n">
-        <v>100</v>
+        <v>96.47</v>
       </c>
       <c r="L53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
         <v>100</v>
       </c>
       <c r="O53" t="n">
-        <v>90.56</v>
+        <v>100</v>
       </c>
       <c r="P53" t="n">
-        <v>94.3</v>
+        <v>75.44</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R53" t="n">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN (007208)</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666503)</t>
         </is>
       </c>
     </row>

--- a/data/IKPA_SEPTEMBER_2025.xlsx
+++ b/data/IKPA_SEPTEMBER_2025.xlsx
@@ -642,7 +642,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -651,17 +651,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -721,7 +721,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA (403409)</t>
+          <t>RUTAN KELAS II B BATURAJA (692339)</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -732,7 +732,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -741,17 +741,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -773,10 +773,10 @@
         <v>100</v>
       </c>
       <c r="L4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
@@ -785,11 +785,11 @@
         <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA (401945)</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA (527975)</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -822,7 +822,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -831,17 +831,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>440507</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -863,10 +863,10 @@
         <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
@@ -875,11 +875,11 @@
         <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA (692339)</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440507)</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -912,7 +912,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -921,17 +921,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>402268</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -991,7 +991,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA (402268)</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU (428258)</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1002,7 +1002,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1011,17 +1011,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA (402267)</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA (410574)</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1092,7 +1092,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1101,17 +1101,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>403409</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA (410574)</t>
+          <t>PENGADILAN AGAMA MARTAPURA (403409)</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1182,7 +1182,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1191,17 +1191,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>402268</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU (428258)</t>
+          <t>PENGADILAN AGAMA BATURAJA (402268)</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1272,7 +1272,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1281,17 +1281,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>440507</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1313,10 +1313,10 @@
         <v>100</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N10" t="n">
         <v>100</v>
@@ -1325,11 +1325,11 @@
         <v>100</v>
       </c>
       <c r="P10" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R10" t="n">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440507)</t>
+          <t>PENGADILAN AGAMA BATURAJA (402267)</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1362,7 +1362,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1371,17 +1371,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1403,10 +1403,10 @@
         <v>100</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N11" t="n">
         <v>100</v>
@@ -1415,11 +1415,11 @@
         <v>100</v>
       </c>
       <c r="P11" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R11" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA (527975)</t>
+          <t>PENGADILAN AGAMA MUARADUA (401945)</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5052,7 +5052,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -5061,55 +5061,55 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>87.17</v>
+        <v>88.88</v>
       </c>
       <c r="G52" t="n">
-        <v>98.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="H52" t="n">
-        <v>100</v>
+        <v>90.56</v>
       </c>
       <c r="I52" t="n">
         <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>74.33</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>96.47</v>
+        <v>100</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N52" t="n">
         <v>100</v>
       </c>
       <c r="O52" t="n">
-        <v>100</v>
+        <v>90.56</v>
       </c>
       <c r="P52" t="n">
-        <v>75.44</v>
+        <v>94.3</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R52" t="n">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666503)</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN (007208)</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
@@ -5142,7 +5142,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -5151,55 +5151,55 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>88.88</v>
+        <v>87.17</v>
       </c>
       <c r="G53" t="n">
-        <v>100</v>
+        <v>98.23999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>90.56</v>
+        <v>100</v>
       </c>
       <c r="I53" t="n">
         <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>77.76000000000001</v>
+        <v>74.33</v>
       </c>
       <c r="K53" t="n">
-        <v>100</v>
+        <v>96.47</v>
       </c>
       <c r="L53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
         <v>100</v>
       </c>
       <c r="O53" t="n">
-        <v>90.56</v>
+        <v>100</v>
       </c>
       <c r="P53" t="n">
-        <v>94.3</v>
+        <v>75.44</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R53" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN (007208)</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666503)</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">

--- a/data/IKPA_SEPTEMBER_2025.xlsx
+++ b/data/IKPA_SEPTEMBER_2025.xlsx
@@ -642,7 +642,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -651,17 +651,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>403409</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -721,7 +721,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA (692339)</t>
+          <t>PENGADILAN AGAMA MARTAPURA (403409)</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -732,7 +732,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -741,17 +741,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -773,10 +773,10 @@
         <v>100</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
@@ -785,11 +785,11 @@
         <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA (527975)</t>
+          <t>PENGADILAN AGAMA MUARADUA (401945)</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -822,7 +822,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -831,17 +831,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>440507</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -863,10 +863,10 @@
         <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
@@ -875,11 +875,11 @@
         <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440507)</t>
+          <t>RUTAN KELAS II B BATURAJA (692339)</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -912,7 +912,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -921,17 +921,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>402268</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -991,7 +991,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU (428258)</t>
+          <t>PENGADILAN AGAMA BATURAJA (402268)</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1002,7 +1002,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1011,17 +1011,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA (410574)</t>
+          <t>PENGADILAN AGAMA BATURAJA (402267)</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1092,7 +1092,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1101,17 +1101,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA (403409)</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA (410574)</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1182,7 +1182,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1191,17 +1191,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>402268</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA (402268)</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU (428258)</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1272,7 +1272,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1281,17 +1281,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>440507</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1313,10 +1313,10 @@
         <v>100</v>
       </c>
       <c r="L10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>100</v>
@@ -1325,11 +1325,11 @@
         <v>100</v>
       </c>
       <c r="P10" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R10" t="n">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA (402267)</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN (440507)</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1362,7 +1362,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1371,17 +1371,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1403,10 +1403,10 @@
         <v>100</v>
       </c>
       <c r="L11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>100</v>
@@ -1415,11 +1415,11 @@
         <v>100</v>
       </c>
       <c r="P11" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R11" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA (401945)</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA (527975)</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5052,7 +5052,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -5061,55 +5061,55 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>88.88</v>
+        <v>87.17</v>
       </c>
       <c r="G52" t="n">
-        <v>100</v>
+        <v>98.23999999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>90.56</v>
+        <v>100</v>
       </c>
       <c r="I52" t="n">
         <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>77.76000000000001</v>
+        <v>74.33</v>
       </c>
       <c r="K52" t="n">
-        <v>100</v>
+        <v>96.47</v>
       </c>
       <c r="L52" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
         <v>100</v>
       </c>
       <c r="O52" t="n">
-        <v>90.56</v>
+        <v>100</v>
       </c>
       <c r="P52" t="n">
-        <v>94.3</v>
+        <v>75.44</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R52" t="n">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN (007208)</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666503)</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
@@ -5142,7 +5142,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -5151,55 +5151,55 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>87.17</v>
+        <v>88.88</v>
       </c>
       <c r="G53" t="n">
-        <v>98.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>90.56</v>
       </c>
       <c r="I53" t="n">
         <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>74.33</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>96.47</v>
+        <v>100</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N53" t="n">
         <v>100</v>
       </c>
       <c r="O53" t="n">
-        <v>100</v>
+        <v>90.56</v>
       </c>
       <c r="P53" t="n">
-        <v>75.44</v>
+        <v>94.3</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R53" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR (666503)</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN (007208)</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">

--- a/data/IKPA_SEPTEMBER_2025.xlsx
+++ b/data/IKPA_SEPTEMBER_2025.xlsx
@@ -662,7 +662,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -671,17 +671,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>403409</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -741,17 +741,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA (692339)</t>
+          <t>PA MARTAPURA (403409)</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -762,7 +762,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -771,17 +771,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -803,10 +803,10 @@
         <v>100</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
@@ -815,11 +815,11 @@
         <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -841,17 +841,17 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA (527975)</t>
+          <t>PA MUARADUA (401945)</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -862,7 +862,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -871,17 +871,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>440507</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -903,10 +903,10 @@
         <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
@@ -915,11 +915,11 @@
         <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440507)</t>
+          <t>RUTAN KELAS II B BATURAJA (692339)</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -962,7 +962,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -971,17 +971,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>402268</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1041,17 +1041,17 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>BPS OKU (428258)</t>
+          <t>PA BATURAJA (402268)</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1062,7 +1062,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1071,17 +1071,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1141,17 +1141,17 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>KPP BATURAJA (410574)</t>
+          <t>PA BATURAJA (402267)</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1162,7 +1162,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1171,17 +1171,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (403409)</t>
+          <t>KPP BATURAJA (410574)</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1262,7 +1262,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>402268</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1341,17 +1341,17 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402268)</t>
+          <t>BPS OKU (428258)</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1362,7 +1362,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1371,17 +1371,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>440507</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1403,10 +1403,10 @@
         <v>100</v>
       </c>
       <c r="L10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>100</v>
@@ -1415,11 +1415,11 @@
         <v>100</v>
       </c>
       <c r="P10" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R10" t="n">
@@ -1441,17 +1441,17 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402267)</t>
+          <t>KEMENAG OKUS (440507)</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1462,7 +1462,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1471,17 +1471,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1503,10 +1503,10 @@
         <v>100</v>
       </c>
       <c r="L11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>100</v>
@@ -1515,11 +1515,11 @@
         <v>100</v>
       </c>
       <c r="P11" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R11" t="n">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>PA MUARADUA (401945)</t>
+          <t>KPPN BATURAJA (527975)</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -5550,7 +5550,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -5559,55 +5559,55 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>88.88</v>
+        <v>87.17</v>
       </c>
       <c r="G52" t="n">
-        <v>100</v>
+        <v>98.23999999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>90.56</v>
+        <v>100</v>
       </c>
       <c r="I52" t="n">
         <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>77.76000000000001</v>
+        <v>74.33</v>
       </c>
       <c r="K52" t="n">
-        <v>100</v>
+        <v>96.47</v>
       </c>
       <c r="L52" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
         <v>100</v>
       </c>
       <c r="O52" t="n">
-        <v>90.56</v>
+        <v>100</v>
       </c>
       <c r="P52" t="n">
-        <v>94.3</v>
+        <v>75.44</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R52" t="n">
@@ -5627,15 +5627,19 @@
       <c r="V52" t="n">
         <v>51</v>
       </c>
-      <c r="W52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT</t>
+        </is>
+      </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN (007208)</t>
+          <t>KEMENAG OKUT (666503)</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
@@ -5646,7 +5650,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -5655,55 +5659,55 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>87.17</v>
+        <v>88.88</v>
       </c>
       <c r="G53" t="n">
-        <v>98.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>90.56</v>
       </c>
       <c r="I53" t="n">
         <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>74.33</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>96.47</v>
+        <v>100</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N53" t="n">
         <v>100</v>
       </c>
       <c r="O53" t="n">
-        <v>100</v>
+        <v>90.56</v>
       </c>
       <c r="P53" t="n">
-        <v>75.44</v>
+        <v>94.3</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R53" t="n">
@@ -5723,19 +5727,15 @@
       <c r="V53" t="n">
         <v>52</v>
       </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUT</t>
-        </is>
-      </c>
+      <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666503)</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN (007208)</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">

--- a/data/IKPA_SEPTEMBER_2025.xlsx
+++ b/data/IKPA_SEPTEMBER_2025.xlsx
@@ -3076,7 +3076,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>'007130</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>'007190</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>'098963</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>'007208</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>'099228</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">

--- a/data/IKPA_SEPTEMBER_2025.xlsx
+++ b/data/IKPA_SEPTEMBER_2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z69"/>
+  <dimension ref="A1:Z74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3139,15 +3139,19 @@
       <c r="V27" t="n">
         <v>26</v>
       </c>
-      <c r="W27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>KEJARI  OKU</t>
+        </is>
+      </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU (007130)</t>
+          <t>KEJARI  OKU ('007130)</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3158,7 +3162,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3167,24 +3171,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>'007130</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>91.29000000000001</v>
+        <v>90.34</v>
       </c>
       <c r="G28" t="n">
-        <v>100</v>
+        <v>99.89</v>
       </c>
       <c r="H28" t="n">
         <v>100</v>
@@ -3193,16 +3197,16 @@
         <v>100</v>
       </c>
       <c r="J28" t="n">
-        <v>82.56999999999999</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>100</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N28" t="n">
         <v>100</v>
@@ -3211,18 +3215,18 @@
         <v>100</v>
       </c>
       <c r="P28" t="n">
-        <v>77.39</v>
+        <v>97.02</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>96.73</v>
+        <v>97.02</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3233,21 +3237,21 @@
         <v>2025</v>
       </c>
       <c r="V28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT (418471)</t>
+          <t>KEJARI  OKU ('007130)</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -3258,7 +3262,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3267,24 +3271,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>'007190</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>88.95</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>99.95999999999999</v>
+        <v>100</v>
       </c>
       <c r="H29" t="n">
         <v>100</v>
@@ -3293,36 +3297,36 @@
         <v>100</v>
       </c>
       <c r="J29" t="n">
-        <v>77.90000000000001</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="K29" t="n">
         <v>100</v>
       </c>
       <c r="L29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>99.83</v>
+        <v>100</v>
       </c>
       <c r="O29" t="n">
         <v>100</v>
       </c>
       <c r="P29" t="n">
-        <v>96.67</v>
+        <v>77.39</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>96.67</v>
+        <v>96.73</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3333,17 +3337,21 @@
         <v>2025</v>
       </c>
       <c r="V29" t="n">
-        <v>28</v>
-      </c>
-      <c r="W29" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>MTSN 2 OKUT</t>
+        </is>
+      </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR (007190)</t>
+          <t>MTSN 2 OKUT (418471)</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -3354,7 +3362,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3363,24 +3371,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>'007190</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>91.03</v>
+        <v>88.95</v>
       </c>
       <c r="G30" t="n">
-        <v>98.33</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="H30" t="n">
         <v>100</v>
@@ -3389,25 +3397,25 @@
         <v>100</v>
       </c>
       <c r="J30" t="n">
-        <v>82.05</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K30" t="n">
         <v>100</v>
       </c>
       <c r="L30" t="n">
-        <v>93.33</v>
+        <v>100</v>
       </c>
       <c r="M30" t="n">
         <v>100</v>
       </c>
       <c r="N30" t="n">
-        <v>100</v>
+        <v>99.83</v>
       </c>
       <c r="O30" t="n">
         <v>100</v>
       </c>
       <c r="P30" t="n">
-        <v>96.64</v>
+        <v>96.67</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -3418,7 +3426,7 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>96.64</v>
+        <v>96.67</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3429,21 +3437,21 @@
         <v>2025</v>
       </c>
       <c r="V30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>KPU OKUT (656560)</t>
+          <t>KEJARI OKUT ('007190)</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -3454,7 +3462,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3463,24 +3471,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>666505</t>
+          <t>'007190</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>91.04000000000001</v>
+        <v>88.95</v>
       </c>
       <c r="G31" t="n">
-        <v>100</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="H31" t="n">
         <v>100</v>
@@ -3489,36 +3497,36 @@
         <v>100</v>
       </c>
       <c r="J31" t="n">
-        <v>82.08</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K31" t="n">
         <v>100</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N31" t="n">
-        <v>100</v>
+        <v>99.83</v>
       </c>
       <c r="O31" t="n">
         <v>100</v>
       </c>
       <c r="P31" t="n">
-        <v>77.31</v>
+        <v>96.67</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>96.64</v>
+        <v>96.67</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3529,21 +3537,21 @@
         <v>2025</v>
       </c>
       <c r="V31" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666505)</t>
+          <t>KEJARI OKUT ('007190)</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -3554,7 +3562,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -3563,24 +3571,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>'098963</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>88.64</v>
+        <v>91.03</v>
       </c>
       <c r="G32" t="n">
-        <v>100</v>
+        <v>98.33</v>
       </c>
       <c r="H32" t="n">
         <v>100</v>
@@ -3589,13 +3597,13 @@
         <v>100</v>
       </c>
       <c r="J32" t="n">
-        <v>77.27</v>
+        <v>82.05</v>
       </c>
       <c r="K32" t="n">
         <v>100</v>
       </c>
       <c r="L32" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="M32" t="n">
         <v>100</v>
@@ -3607,7 +3615,7 @@
         <v>100</v>
       </c>
       <c r="P32" t="n">
-        <v>96.59</v>
+        <v>96.64</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -3618,7 +3626,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>96.59</v>
+        <v>96.64</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3629,17 +3637,21 @@
         <v>2025</v>
       </c>
       <c r="V32" t="n">
-        <v>31</v>
-      </c>
-      <c r="W32" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>KPU OKUT</t>
+        </is>
+      </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA (098963)</t>
+          <t>KPU OKUT (656560)</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -3650,7 +3662,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -3659,24 +3671,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>666505</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>88.41</v>
+        <v>91.04000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>99.86</v>
+        <v>100</v>
       </c>
       <c r="H33" t="n">
         <v>100</v>
@@ -3685,16 +3697,16 @@
         <v>100</v>
       </c>
       <c r="J33" t="n">
-        <v>76.81</v>
+        <v>82.08</v>
       </c>
       <c r="K33" t="n">
-        <v>99.45</v>
+        <v>100</v>
       </c>
       <c r="L33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>100</v>
@@ -3703,18 +3715,18 @@
         <v>100</v>
       </c>
       <c r="P33" t="n">
-        <v>96.41</v>
+        <v>77.31</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>96.41</v>
+        <v>96.64</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3725,21 +3737,21 @@
         <v>2025</v>
       </c>
       <c r="V33" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA (692334)</t>
+          <t>KEMENAG OKUT (666505)</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -3750,7 +3762,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -3759,24 +3771,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>'098963</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>94.77</v>
+        <v>88.64</v>
       </c>
       <c r="G34" t="n">
-        <v>94.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="H34" t="n">
         <v>100</v>
@@ -3785,25 +3797,25 @@
         <v>100</v>
       </c>
       <c r="J34" t="n">
-        <v>89.53</v>
+        <v>77.27</v>
       </c>
       <c r="K34" t="n">
         <v>100</v>
       </c>
       <c r="L34" t="n">
-        <v>93.33</v>
+        <v>100</v>
       </c>
       <c r="M34" t="n">
         <v>100</v>
       </c>
       <c r="N34" t="n">
-        <v>84.95999999999999</v>
+        <v>100</v>
       </c>
       <c r="O34" t="n">
         <v>100</v>
       </c>
       <c r="P34" t="n">
-        <v>96.26000000000001</v>
+        <v>96.59</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -3814,7 +3826,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>96.26000000000001</v>
+        <v>96.59</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3825,21 +3837,21 @@
         <v>2025</v>
       </c>
       <c r="V34" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>KPU OKU (656553)</t>
+          <t>PN BATURAJA ('098963)</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -3850,7 +3862,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3859,24 +3871,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>418462</t>
+          <t>'098963</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>90.48999999999999</v>
+        <v>88.64</v>
       </c>
       <c r="G35" t="n">
-        <v>99.51000000000001</v>
+        <v>100</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
@@ -3885,36 +3897,36 @@
         <v>100</v>
       </c>
       <c r="J35" t="n">
-        <v>80.98</v>
+        <v>77.27</v>
       </c>
       <c r="K35" t="n">
-        <v>99.33</v>
+        <v>100</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N35" t="n">
-        <v>99.69</v>
+        <v>100</v>
       </c>
       <c r="O35" t="n">
         <v>100</v>
       </c>
       <c r="P35" t="n">
-        <v>76.98</v>
+        <v>96.59</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>96.23</v>
+        <v>96.59</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3925,21 +3937,21 @@
         <v>2025</v>
       </c>
       <c r="V35" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS (418462)</t>
+          <t>PN BATURAJA ('098963)</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -3950,7 +3962,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -3964,19 +3976,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>692340</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MARTAPURA</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>88.04000000000001</v>
+        <v>88.41</v>
       </c>
       <c r="G36" t="n">
-        <v>99.76000000000001</v>
+        <v>99.86</v>
       </c>
       <c r="H36" t="n">
         <v>100</v>
@@ -3985,10 +3997,10 @@
         <v>100</v>
       </c>
       <c r="J36" t="n">
-        <v>76.08</v>
+        <v>76.81</v>
       </c>
       <c r="K36" t="n">
-        <v>99.05</v>
+        <v>99.45</v>
       </c>
       <c r="L36" t="n">
         <v>100</v>
@@ -4003,7 +4015,7 @@
         <v>100</v>
       </c>
       <c r="P36" t="n">
-        <v>96.22</v>
+        <v>96.41</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -4014,7 +4026,7 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>96.22</v>
+        <v>96.41</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4025,21 +4037,21 @@
         <v>2025</v>
       </c>
       <c r="V36" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA (692340)</t>
+          <t>LAPAS MUARA DUA (692334)</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -4050,7 +4062,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4059,24 +4071,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>86.95</v>
+        <v>94.77</v>
       </c>
       <c r="G37" t="n">
-        <v>100</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
@@ -4085,25 +4097,25 @@
         <v>100</v>
       </c>
       <c r="J37" t="n">
-        <v>73.89</v>
+        <v>89.53</v>
       </c>
       <c r="K37" t="n">
         <v>100</v>
       </c>
       <c r="L37" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="M37" t="n">
         <v>100</v>
       </c>
       <c r="N37" t="n">
-        <v>100</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="O37" t="n">
         <v>100</v>
       </c>
       <c r="P37" t="n">
-        <v>96.08</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -4114,7 +4126,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>96.08</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4125,21 +4137,21 @@
         <v>2025</v>
       </c>
       <c r="V37" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>BPN OKUS (670561)</t>
+          <t>KPU OKU (656553)</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -4150,7 +4162,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4164,19 +4176,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>666504</t>
+          <t>418462</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>96.06</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>93.34</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="H38" t="n">
         <v>100</v>
@@ -4185,10 +4197,10 @@
         <v>100</v>
       </c>
       <c r="J38" t="n">
-        <v>92.11</v>
+        <v>80.98</v>
       </c>
       <c r="K38" t="n">
-        <v>93.03</v>
+        <v>99.33</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -4197,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>93.65000000000001</v>
+        <v>99.69</v>
       </c>
       <c r="O38" t="n">
         <v>100</v>
       </c>
       <c r="P38" t="n">
-        <v>76.79000000000001</v>
+        <v>76.98</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -4214,7 +4226,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>95.98</v>
+        <v>96.23</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4225,21 +4237,21 @@
         <v>2025</v>
       </c>
       <c r="V38" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666504)</t>
+          <t>MTSN 2 OKUS (418462)</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -4250,7 +4262,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4259,62 +4271,62 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>661192</t>
+          <t>692340</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+          <t>LAPAS KELAS II B MARTAPURA</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>90.94</v>
+        <v>88.04000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>99.92</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>97.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="I39" t="n">
         <v>100</v>
       </c>
       <c r="J39" t="n">
-        <v>81.88</v>
+        <v>76.08</v>
       </c>
       <c r="K39" t="n">
-        <v>100</v>
+        <v>99.05</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N39" t="n">
-        <v>99.83</v>
+        <v>100</v>
       </c>
       <c r="O39" t="n">
-        <v>97.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="P39" t="n">
-        <v>76.66</v>
+        <v>96.22</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>95.81999999999999</v>
+        <v>96.22</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4325,21 +4337,21 @@
         <v>2025</v>
       </c>
       <c r="V39" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS (661192)</t>
+          <t>LAPAS MARTAPURA (692340)</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -4350,7 +4362,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -4359,24 +4371,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>670561</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>91.84999999999999</v>
+        <v>86.95</v>
       </c>
       <c r="G40" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H40" t="n">
         <v>100</v>
@@ -4385,36 +4397,36 @@
         <v>100</v>
       </c>
       <c r="J40" t="n">
-        <v>83.69</v>
+        <v>73.89</v>
       </c>
       <c r="K40" t="n">
-        <v>99.94</v>
+        <v>100</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N40" t="n">
-        <v>90.06999999999999</v>
+        <v>100</v>
       </c>
       <c r="O40" t="n">
         <v>100</v>
       </c>
       <c r="P40" t="n">
-        <v>76.55</v>
+        <v>96.08</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>95.69</v>
+        <v>96.08</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4425,21 +4437,21 @@
         <v>2025</v>
       </c>
       <c r="V40" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>KPU OKUS (656574)</t>
+          <t>BPN OKUS (670561)</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -4450,7 +4462,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -4464,31 +4476,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>440503</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>96.94</v>
+        <v>96.06</v>
       </c>
       <c r="G41" t="n">
-        <v>96.44</v>
+        <v>93.34</v>
       </c>
       <c r="H41" t="n">
-        <v>95.56</v>
+        <v>100</v>
       </c>
       <c r="I41" t="n">
         <v>100</v>
       </c>
       <c r="J41" t="n">
-        <v>93.88</v>
+        <v>92.11</v>
       </c>
       <c r="K41" t="n">
-        <v>92.88</v>
+        <v>93.03</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -4497,13 +4509,13 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>100</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>95.56</v>
+        <v>100</v>
       </c>
       <c r="P41" t="n">
-        <v>76.55</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -4514,7 +4526,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>95.68000000000001</v>
+        <v>95.98</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4525,21 +4537,21 @@
         <v>2025</v>
       </c>
       <c r="V41" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440503)</t>
+          <t>KEMENAG OKUT (666504)</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
@@ -4550,7 +4562,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -4564,57 +4576,57 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>661192</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>89.84999999999999</v>
+        <v>90.94</v>
       </c>
       <c r="G42" t="n">
-        <v>98.28</v>
+        <v>99.92</v>
       </c>
       <c r="H42" t="n">
-        <v>100</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="I42" t="n">
         <v>100</v>
       </c>
       <c r="J42" t="n">
-        <v>79.69</v>
+        <v>81.88</v>
       </c>
       <c r="K42" t="n">
-        <v>93.11</v>
+        <v>100</v>
       </c>
       <c r="L42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>100</v>
+        <v>99.83</v>
       </c>
       <c r="O42" t="n">
-        <v>100</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="P42" t="n">
-        <v>95.58</v>
+        <v>76.66</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>95.58</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4625,21 +4637,21 @@
         <v>2025</v>
       </c>
       <c r="V42" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT (424967)</t>
+          <t>MTSN 4 OKUS (661192)</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
@@ -4650,7 +4662,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -4659,24 +4671,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>85.41</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>99.68000000000001</v>
+        <v>95</v>
       </c>
       <c r="H43" t="n">
         <v>100</v>
@@ -4685,36 +4697,36 @@
         <v>100</v>
       </c>
       <c r="J43" t="n">
-        <v>70.81999999999999</v>
+        <v>83.69</v>
       </c>
       <c r="K43" t="n">
-        <v>100</v>
+        <v>99.94</v>
       </c>
       <c r="L43" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>98.70999999999999</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="O43" t="n">
         <v>100</v>
       </c>
       <c r="P43" t="n">
-        <v>95.48999999999999</v>
+        <v>76.55</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>95.48999999999999</v>
+        <v>95.69</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4725,21 +4737,21 @@
         <v>2025</v>
       </c>
       <c r="V43" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>BPN OKU (431142)</t>
+          <t>KPU OKUS (656574)</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
@@ -4750,7 +4762,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -4764,7 +4776,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>440502</t>
+          <t>440503</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4773,22 +4785,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>89.34</v>
+        <v>96.94</v>
       </c>
       <c r="G44" t="n">
-        <v>97.22</v>
+        <v>96.44</v>
       </c>
       <c r="H44" t="n">
-        <v>100</v>
+        <v>95.56</v>
       </c>
       <c r="I44" t="n">
         <v>100</v>
       </c>
       <c r="J44" t="n">
-        <v>78.68000000000001</v>
+        <v>93.88</v>
       </c>
       <c r="K44" t="n">
-        <v>100</v>
+        <v>92.88</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -4797,13 +4809,13 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="O44" t="n">
-        <v>100</v>
+        <v>95.56</v>
       </c>
       <c r="P44" t="n">
-        <v>76.25</v>
+        <v>76.55</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -4814,7 +4826,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>95.31</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4825,7 +4837,7 @@
         <v>2025</v>
       </c>
       <c r="V44" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -4839,7 +4851,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440502)</t>
+          <t>KEMENAG OKUS (440503)</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
@@ -4850,7 +4862,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -4864,19 +4876,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>424967</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>88.01000000000001</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>97.86</v>
+        <v>98.28</v>
       </c>
       <c r="H45" t="n">
         <v>100</v>
@@ -4885,36 +4897,36 @@
         <v>100</v>
       </c>
       <c r="J45" t="n">
-        <v>76.01000000000001</v>
+        <v>79.69</v>
       </c>
       <c r="K45" t="n">
-        <v>100</v>
+        <v>93.11</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N45" t="n">
-        <v>95.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="O45" t="n">
         <v>100</v>
       </c>
       <c r="P45" t="n">
-        <v>75.97</v>
+        <v>95.58</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>94.97</v>
+        <v>95.58</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4925,21 +4937,21 @@
         <v>2025</v>
       </c>
       <c r="V45" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU (426050)</t>
+          <t>MTSN 1 OKUT (424967)</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
@@ -4950,7 +4962,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -4959,24 +4971,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>692725</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RUPBASAN KELAS II BATURAJA</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>87.90000000000001</v>
+        <v>85.41</v>
       </c>
       <c r="G46" t="n">
-        <v>97.31999999999999</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="H46" t="n">
         <v>100</v>
@@ -4985,10 +4997,10 @@
         <v>100</v>
       </c>
       <c r="J46" t="n">
-        <v>75.79000000000001</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>96.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="L46" t="n">
         <v>100</v>
@@ -4997,13 +5009,13 @@
         <v>100</v>
       </c>
       <c r="N46" t="n">
-        <v>92.86</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="O46" t="n">
         <v>100</v>
       </c>
       <c r="P46" t="n">
-        <v>94.94</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -5014,7 +5026,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>94.94</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5025,21 +5037,21 @@
         <v>2025</v>
       </c>
       <c r="V46" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>RUPBASAN BATURAJA</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>RUPBASAN BATURAJA</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>RUPBASAN BATURAJA (692725)</t>
+          <t>BPN OKU (431142)</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
@@ -5050,7 +5062,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -5064,19 +5076,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>597558</t>
+          <t>440502</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>87.89</v>
+        <v>89.34</v>
       </c>
       <c r="G47" t="n">
-        <v>97.77</v>
+        <v>97.22</v>
       </c>
       <c r="H47" t="n">
         <v>100</v>
@@ -5085,7 +5097,7 @@
         <v>100</v>
       </c>
       <c r="J47" t="n">
-        <v>75.77</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="K47" t="n">
         <v>100</v>
@@ -5097,13 +5109,13 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>95.54000000000001</v>
+        <v>94.44</v>
       </c>
       <c r="O47" t="n">
         <v>100</v>
       </c>
       <c r="P47" t="n">
-        <v>75.92</v>
+        <v>76.25</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -5114,7 +5126,7 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>94.90000000000001</v>
+        <v>95.31</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5125,21 +5137,21 @@
         <v>2025</v>
       </c>
       <c r="V47" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS (597558)</t>
+          <t>KEMENAG OKUS (440502)</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
@@ -5150,7 +5162,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -5164,28 +5176,28 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>662127</t>
+          <t>426050</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>91.01000000000001</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>100</v>
+        <v>97.86</v>
       </c>
       <c r="H48" t="n">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="I48" t="n">
         <v>100</v>
       </c>
       <c r="J48" t="n">
-        <v>82.01000000000001</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="K48" t="n">
         <v>100</v>
@@ -5197,13 +5209,13 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>100</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="O48" t="n">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="P48" t="n">
-        <v>75.87</v>
+        <v>75.97</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -5214,7 +5226,7 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>94.84</v>
+        <v>94.97</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5225,21 +5237,21 @@
         <v>2025</v>
       </c>
       <c r="V48" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS (662127)</t>
+          <t>MTSN 1 OKU (426050)</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -5250,7 +5262,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -5259,24 +5271,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>692725</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>RUPBASAN KELAS II BATURAJA</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>87.55</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>97.56</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="H49" t="n">
         <v>100</v>
@@ -5285,25 +5297,25 @@
         <v>100</v>
       </c>
       <c r="J49" t="n">
-        <v>75.09</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>94.88</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>95.55</v>
+        <v>100</v>
       </c>
       <c r="M49" t="n">
         <v>100</v>
       </c>
       <c r="N49" t="n">
-        <v>99.79000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="O49" t="n">
         <v>100</v>
       </c>
       <c r="P49" t="n">
-        <v>94.77</v>
+        <v>94.94</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -5314,7 +5326,7 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>94.77</v>
+        <v>94.94</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5325,21 +5337,21 @@
         <v>2025</v>
       </c>
       <c r="V49" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>RUPBASAN BATURAJA</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>RUPBASAN BATURAJA</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT (426066)</t>
+          <t>RUPBASAN BATURAJA (692725)</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
@@ -5350,7 +5362,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -5364,19 +5376,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>597558</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>85.56999999999999</v>
+        <v>87.89</v>
       </c>
       <c r="G50" t="n">
-        <v>100</v>
+        <v>97.77</v>
       </c>
       <c r="H50" t="n">
         <v>100</v>
@@ -5385,7 +5397,7 @@
         <v>100</v>
       </c>
       <c r="J50" t="n">
-        <v>71.14</v>
+        <v>75.77</v>
       </c>
       <c r="K50" t="n">
         <v>100</v>
@@ -5397,13 +5409,13 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>100</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="O50" t="n">
         <v>100</v>
       </c>
       <c r="P50" t="n">
-        <v>75.67</v>
+        <v>75.92</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -5414,7 +5426,7 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>94.59</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5425,21 +5437,21 @@
         <v>2025</v>
       </c>
       <c r="V50" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418459)</t>
+          <t>MAN 2 OKUS (597558)</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
@@ -5450,7 +5462,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -5464,31 +5476,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>662127</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>90.42</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>96.25</v>
+        <v>100</v>
       </c>
       <c r="H51" t="n">
-        <v>100</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="I51" t="n">
         <v>100</v>
       </c>
       <c r="J51" t="n">
-        <v>80.83</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>92.48999999999999</v>
+        <v>100</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -5500,10 +5512,10 @@
         <v>100</v>
       </c>
       <c r="O51" t="n">
-        <v>100</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="P51" t="n">
-        <v>75.62</v>
+        <v>75.87</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -5514,7 +5526,7 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>94.53</v>
+        <v>94.84</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5525,21 +5537,21 @@
         <v>2025</v>
       </c>
       <c r="V51" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS (553792)</t>
+          <t>MAN 1 OKUS (662127)</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
@@ -5550,7 +5562,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -5564,19 +5576,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>426066</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>87.17</v>
+        <v>87.55</v>
       </c>
       <c r="G52" t="n">
-        <v>98.23999999999999</v>
+        <v>97.56</v>
       </c>
       <c r="H52" t="n">
         <v>100</v>
@@ -5585,36 +5597,36 @@
         <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>74.33</v>
+        <v>75.09</v>
       </c>
       <c r="K52" t="n">
-        <v>96.47</v>
+        <v>94.88</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>95.55</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N52" t="n">
-        <v>100</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="O52" t="n">
         <v>100</v>
       </c>
       <c r="P52" t="n">
-        <v>75.44</v>
+        <v>94.77</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>94.3</v>
+        <v>94.77</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5625,21 +5637,21 @@
         <v>2025</v>
       </c>
       <c r="V52" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666503)</t>
+          <t>MAN 1 OKUT (426066)</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
@@ -5650,7 +5662,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -5659,62 +5671,62 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>'007208</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>88.88</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="G53" t="n">
         <v>100</v>
       </c>
       <c r="H53" t="n">
-        <v>90.56</v>
+        <v>100</v>
       </c>
       <c r="I53" t="n">
         <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>77.76000000000001</v>
+        <v>71.14</v>
       </c>
       <c r="K53" t="n">
         <v>100</v>
       </c>
       <c r="L53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
         <v>100</v>
       </c>
       <c r="O53" t="n">
-        <v>90.56</v>
+        <v>100</v>
       </c>
       <c r="P53" t="n">
-        <v>94.3</v>
+        <v>75.67</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>94.3</v>
+        <v>94.59</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5725,17 +5737,21 @@
         <v>2025</v>
       </c>
       <c r="V53" t="n">
-        <v>52</v>
-      </c>
-      <c r="W53" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU</t>
+        </is>
+      </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN (007208)</t>
+          <t>KEMENAG OKU (418459)</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
@@ -5746,7 +5762,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -5760,19 +5776,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>418458</t>
+          <t>553792</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>89.75</v>
+        <v>90.42</v>
       </c>
       <c r="G54" t="n">
-        <v>95.02</v>
+        <v>96.25</v>
       </c>
       <c r="H54" t="n">
         <v>100</v>
@@ -5781,10 +5797,10 @@
         <v>100</v>
       </c>
       <c r="J54" t="n">
-        <v>79.48999999999999</v>
+        <v>80.83</v>
       </c>
       <c r="K54" t="n">
-        <v>94.84</v>
+        <v>92.48999999999999</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -5793,13 +5809,13 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="O54" t="n">
         <v>100</v>
       </c>
       <c r="P54" t="n">
-        <v>75.41</v>
+        <v>75.62</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -5810,7 +5826,7 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>94.26000000000001</v>
+        <v>94.53</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5821,21 +5837,21 @@
         <v>2025</v>
       </c>
       <c r="V54" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418458)</t>
+          <t>MTSN 1 OKUS (553792)</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
@@ -5846,7 +5862,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -5855,62 +5871,62 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>84.92</v>
+        <v>87.17</v>
       </c>
       <c r="G55" t="n">
-        <v>99.25</v>
+        <v>98.23999999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>96.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="I55" t="n">
         <v>100</v>
       </c>
       <c r="J55" t="n">
-        <v>69.84</v>
+        <v>74.33</v>
       </c>
       <c r="K55" t="n">
-        <v>98.58</v>
+        <v>96.47</v>
       </c>
       <c r="L55" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="O55" t="n">
-        <v>96.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="P55" t="n">
-        <v>94.20999999999999</v>
+        <v>75.44</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>94.20999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5921,21 +5937,21 @@
         <v>2025</v>
       </c>
       <c r="V55" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR (344894)</t>
+          <t>KEMENAG OKUT (666503)</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
@@ -5946,7 +5962,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -5955,62 +5971,62 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>'007208</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>84.98999999999999</v>
+        <v>88.88</v>
       </c>
       <c r="G56" t="n">
-        <v>99.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="H56" t="n">
-        <v>100</v>
+        <v>90.56</v>
       </c>
       <c r="I56" t="n">
         <v>100</v>
       </c>
       <c r="J56" t="n">
-        <v>69.98</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="K56" t="n">
         <v>100</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N56" t="n">
-        <v>98.48999999999999</v>
+        <v>100</v>
       </c>
       <c r="O56" t="n">
-        <v>100</v>
+        <v>90.56</v>
       </c>
       <c r="P56" t="n">
-        <v>75.34999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>94.18000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6021,21 +6037,21 @@
         <v>2025</v>
       </c>
       <c r="V56" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>KEJARI  OKUS</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>KEJARI  OKUS</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>BNN OKUT (111079)</t>
+          <t>KEJARI  OKUS ('007208)</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
@@ -6046,7 +6062,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -6055,36 +6071,36 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>'007208</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>88.73</v>
+        <v>88.88</v>
       </c>
       <c r="G57" t="n">
-        <v>96.87</v>
+        <v>100</v>
       </c>
       <c r="H57" t="n">
-        <v>98.09</v>
+        <v>90.56</v>
       </c>
       <c r="I57" t="n">
         <v>100</v>
       </c>
       <c r="J57" t="n">
-        <v>77.45999999999999</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>91.69</v>
+        <v>100</v>
       </c>
       <c r="L57" t="n">
         <v>100</v>
@@ -6093,13 +6109,13 @@
         <v>100</v>
       </c>
       <c r="N57" t="n">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="O57" t="n">
-        <v>98.09</v>
+        <v>90.56</v>
       </c>
       <c r="P57" t="n">
-        <v>94.06</v>
+        <v>94.3</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -6110,7 +6126,7 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>94.06</v>
+        <v>94.3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6121,21 +6137,21 @@
         <v>2025</v>
       </c>
       <c r="V57" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>KEJARI  OKUS</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>KEJARI  OKUS</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS (690801)</t>
+          <t>KEJARI  OKUS ('007208)</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
@@ -6146,7 +6162,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -6160,31 +6176,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>666501</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>93.34999999999999</v>
+        <v>89.75</v>
       </c>
       <c r="G58" t="n">
-        <v>92.01000000000001</v>
+        <v>95.02</v>
       </c>
       <c r="H58" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="I58" t="n">
         <v>100</v>
       </c>
       <c r="J58" t="n">
-        <v>86.7</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="K58" t="n">
-        <v>99.98999999999999</v>
+        <v>94.84</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -6193,13 +6209,13 @@
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>84.03</v>
+        <v>95.2</v>
       </c>
       <c r="O58" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="P58" t="n">
-        <v>74.66</v>
+        <v>75.41</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -6210,7 +6226,7 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>93.31999999999999</v>
+        <v>94.26000000000001</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6221,21 +6237,21 @@
         <v>2025</v>
       </c>
       <c r="V58" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666501)</t>
+          <t>KEMENAG OKU (418458)</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
@@ -6246,7 +6262,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -6255,36 +6271,36 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>344894</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>84.26000000000001</v>
+        <v>84.92</v>
       </c>
       <c r="G59" t="n">
-        <v>94.76000000000001</v>
+        <v>99.25</v>
       </c>
       <c r="H59" t="n">
-        <v>100</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="I59" t="n">
         <v>100</v>
       </c>
       <c r="J59" t="n">
-        <v>68.52</v>
+        <v>69.84</v>
       </c>
       <c r="K59" t="n">
-        <v>100</v>
+        <v>98.58</v>
       </c>
       <c r="L59" t="n">
         <v>100</v>
@@ -6293,13 +6309,13 @@
         <v>100</v>
       </c>
       <c r="N59" t="n">
-        <v>79.02</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O59" t="n">
-        <v>100</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="P59" t="n">
-        <v>93.18000000000001</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -6310,7 +6326,7 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>93.18000000000001</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6321,21 +6337,21 @@
         <v>2025</v>
       </c>
       <c r="V59" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>BAWASLU OKU (419006)</t>
+          <t>RUMKIT NOESMIR (344894)</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
@@ -6346,7 +6362,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -6355,33 +6371,33 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>066</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>686503</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>86.14</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="G60" t="n">
-        <v>97.13</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>95.63</v>
+        <v>100</v>
       </c>
       <c r="I60" t="n">
         <v>100</v>
       </c>
       <c r="J60" t="n">
-        <v>72.27</v>
+        <v>69.98</v>
       </c>
       <c r="K60" t="n">
         <v>100</v>
@@ -6393,13 +6409,13 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>94.26000000000001</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="O60" t="n">
-        <v>95.63</v>
+        <v>100</v>
       </c>
       <c r="P60" t="n">
-        <v>74.17</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -6410,7 +6426,7 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>92.72</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6421,21 +6437,21 @@
         <v>2025</v>
       </c>
       <c r="V60" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS (686503)</t>
+          <t>BNN OKUT (111079)</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
@@ -6446,7 +6462,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -6455,36 +6471,36 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>024</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>403410</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>95.68000000000001</v>
+        <v>88.73</v>
       </c>
       <c r="G61" t="n">
-        <v>98.63</v>
+        <v>96.87</v>
       </c>
       <c r="H61" t="n">
-        <v>76.67</v>
+        <v>98.09</v>
       </c>
       <c r="I61" t="n">
         <v>100</v>
       </c>
       <c r="J61" t="n">
-        <v>91.36</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>97.59</v>
+        <v>91.69</v>
       </c>
       <c r="L61" t="n">
         <v>100</v>
@@ -6493,13 +6509,13 @@
         <v>100</v>
       </c>
       <c r="N61" t="n">
-        <v>96.92</v>
+        <v>95.8</v>
       </c>
       <c r="O61" t="n">
-        <v>76.67</v>
+        <v>98.09</v>
       </c>
       <c r="P61" t="n">
-        <v>92.08</v>
+        <v>94.06</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -6510,7 +6526,7 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>92.08</v>
+        <v>94.06</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6521,21 +6537,21 @@
         <v>2025</v>
       </c>
       <c r="V61" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>PA  MUARADUA (403410)</t>
+          <t>LOKA LABKESMAS (690801)</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
@@ -6546,7 +6562,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -6560,31 +6576,31 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>666501</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>84.55</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="G62" t="n">
-        <v>91.79000000000001</v>
+        <v>92.01000000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I62" t="n">
         <v>100</v>
       </c>
       <c r="J62" t="n">
-        <v>69.09</v>
+        <v>86.7</v>
       </c>
       <c r="K62" t="n">
-        <v>95.01000000000001</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -6593,13 +6609,13 @@
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>88.56</v>
+        <v>84.03</v>
       </c>
       <c r="O62" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P62" t="n">
-        <v>73.22</v>
+        <v>74.66</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -6610,7 +6626,7 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>91.53</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6621,21 +6637,21 @@
         <v>2025</v>
       </c>
       <c r="V62" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS (574370)</t>
+          <t>KEMENAG OKUT (666501)</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
@@ -6646,7 +6662,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -6655,24 +6671,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>666507</t>
+          <t>419006</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>88.03</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>83.22</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="H63" t="n">
         <v>100</v>
@@ -6681,36 +6697,36 @@
         <v>100</v>
       </c>
       <c r="J63" t="n">
-        <v>76.05</v>
+        <v>68.52</v>
       </c>
       <c r="K63" t="n">
-        <v>86.67</v>
+        <v>100</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N63" t="n">
-        <v>79.76000000000001</v>
+        <v>79.02</v>
       </c>
       <c r="O63" t="n">
         <v>100</v>
       </c>
       <c r="P63" t="n">
-        <v>71.72</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>89.65000000000001</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6721,21 +6737,21 @@
         <v>2025</v>
       </c>
       <c r="V63" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666507)</t>
+          <t>BAWASLU OKU (419006)</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
@@ -6746,7 +6762,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -6755,36 +6771,36 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>'099228</t>
+          <t>686503</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>87.06</v>
+        <v>86.14</v>
       </c>
       <c r="G64" t="n">
-        <v>92.23</v>
+        <v>97.13</v>
       </c>
       <c r="H64" t="n">
-        <v>91.92</v>
+        <v>95.63</v>
       </c>
       <c r="I64" t="n">
         <v>100</v>
       </c>
       <c r="J64" t="n">
-        <v>74.12</v>
+        <v>72.27</v>
       </c>
       <c r="K64" t="n">
-        <v>88.17</v>
+        <v>100</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -6793,13 +6809,13 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>96.29000000000001</v>
+        <v>94.26000000000001</v>
       </c>
       <c r="O64" t="n">
-        <v>91.92</v>
+        <v>95.63</v>
       </c>
       <c r="P64" t="n">
-        <v>71.36</v>
+        <v>74.17</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -6810,7 +6826,7 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>89.2</v>
+        <v>92.72</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6821,17 +6837,21 @@
         <v>2025</v>
       </c>
       <c r="V64" t="n">
-        <v>63</v>
-      </c>
-      <c r="W64" t="inlineStr"/>
+        <v>59</v>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>BAWASLU OKUS</t>
+        </is>
+      </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA (099228)</t>
+          <t>BAWASLU OKUS (686503)</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
@@ -6842,7 +6862,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -6851,62 +6871,62 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>418457</t>
+          <t>403410</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>85.58</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="G65" t="n">
-        <v>84.51000000000001</v>
+        <v>98.63</v>
       </c>
       <c r="H65" t="n">
-        <v>100</v>
+        <v>76.67</v>
       </c>
       <c r="I65" t="n">
         <v>100</v>
       </c>
       <c r="J65" t="n">
-        <v>71.16</v>
+        <v>91.36</v>
       </c>
       <c r="K65" t="n">
-        <v>83.37</v>
+        <v>97.59</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N65" t="n">
-        <v>85.65000000000001</v>
+        <v>96.92</v>
       </c>
       <c r="O65" t="n">
-        <v>100</v>
+        <v>76.67</v>
       </c>
       <c r="P65" t="n">
-        <v>70.91</v>
+        <v>92.08</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>88.64</v>
+        <v>92.08</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6917,21 +6937,21 @@
         <v>2025</v>
       </c>
       <c r="V65" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418457)</t>
+          <t>PA  MUARADUA (403410)</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
@@ -6942,7 +6962,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -6956,31 +6976,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>666502</t>
+          <t>574370</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>84.8</v>
+        <v>84.55</v>
       </c>
       <c r="G66" t="n">
-        <v>92.89</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="H66" t="n">
-        <v>91.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I66" t="n">
         <v>100</v>
       </c>
       <c r="J66" t="n">
-        <v>69.59999999999999</v>
+        <v>69.09</v>
       </c>
       <c r="K66" t="n">
-        <v>86.38</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -6989,13 +7009,13 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>99.40000000000001</v>
+        <v>88.56</v>
       </c>
       <c r="O66" t="n">
-        <v>91.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="P66" t="n">
-        <v>70.63</v>
+        <v>73.22</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -7006,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>88.29000000000001</v>
+        <v>91.53</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7017,21 +7037,21 @@
         <v>2025</v>
       </c>
       <c r="V66" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666502)</t>
+          <t>MTSN 3 OKUS (574370)</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
@@ -7042,7 +7062,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -7056,57 +7076,57 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>666507</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>86.75</v>
+        <v>88.03</v>
       </c>
       <c r="G67" t="n">
-        <v>99.91</v>
+        <v>83.22</v>
       </c>
       <c r="H67" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="I67" t="n">
         <v>100</v>
       </c>
       <c r="J67" t="n">
-        <v>73.5</v>
+        <v>76.05</v>
       </c>
       <c r="K67" t="n">
-        <v>100</v>
+        <v>86.67</v>
       </c>
       <c r="L67" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>99.65000000000001</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="O67" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="P67" t="n">
-        <v>87.23999999999999</v>
+        <v>71.72</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>87.23999999999999</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7117,21 +7137,21 @@
         <v>2025</v>
       </c>
       <c r="V67" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>MAN 1 OKU (424245)</t>
+          <t>KEMENAG OKUT (666507)</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
@@ -7142,7 +7162,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -7151,36 +7171,36 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>418461</t>
+          <t>'099228</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>81.53</v>
+        <v>87.06</v>
       </c>
       <c r="G68" t="n">
-        <v>82.56</v>
+        <v>92.23</v>
       </c>
       <c r="H68" t="n">
-        <v>100</v>
+        <v>91.92</v>
       </c>
       <c r="I68" t="n">
         <v>100</v>
       </c>
       <c r="J68" t="n">
-        <v>63.05</v>
+        <v>74.12</v>
       </c>
       <c r="K68" t="n">
-        <v>70.22</v>
+        <v>88.17</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -7189,13 +7209,13 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>94.90000000000001</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="O68" t="n">
-        <v>100</v>
+        <v>91.92</v>
       </c>
       <c r="P68" t="n">
-        <v>67.98999999999999</v>
+        <v>71.36</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -7206,7 +7226,7 @@
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>84.98999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7217,21 +7237,21 @@
         <v>2025</v>
       </c>
       <c r="V68" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418461)</t>
+          <t>PN BATURAJA ('099228)</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
@@ -7242,7 +7262,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -7251,51 +7271,51 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>691653</t>
+          <t>'099228</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>DINAS TENAGA KERJA DAN TRANSMIGRASI KABUPATEN OKU TIMUR</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>75.8</v>
+        <v>87.06</v>
       </c>
       <c r="G69" t="n">
-        <v>46.99</v>
+        <v>92.23</v>
       </c>
       <c r="H69" t="n">
-        <v>100</v>
+        <v>91.92</v>
       </c>
       <c r="I69" t="n">
         <v>100</v>
       </c>
       <c r="J69" t="n">
-        <v>51.6</v>
+        <v>74.12</v>
       </c>
       <c r="K69" t="n">
-        <v>33.98</v>
+        <v>88.17</v>
       </c>
       <c r="L69" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="O69" t="n">
-        <v>100</v>
+        <v>91.92</v>
       </c>
       <c r="P69" t="n">
-        <v>55.54</v>
+        <v>71.36</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -7306,7 +7326,7 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>69.42</v>
+        <v>89.2</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7317,24 +7337,524 @@
         <v>2025</v>
       </c>
       <c r="V69" t="n">
+        <v>63</v>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>PN BATURAJA</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>PN BATURAJA</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>PN BATURAJA ('099228)</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>64</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>418457</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>85.58</v>
+      </c>
+      <c r="G70" t="n">
+        <v>84.51000000000001</v>
+      </c>
+      <c r="H70" t="n">
+        <v>100</v>
+      </c>
+      <c r="I70" t="n">
+        <v>100</v>
+      </c>
+      <c r="J70" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="K70" t="n">
+        <v>83.37</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>85.65000000000001</v>
+      </c>
+      <c r="O70" t="n">
+        <v>100</v>
+      </c>
+      <c r="P70" t="n">
+        <v>70.91</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>88.64</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>SEPTEMBER</t>
+        </is>
+      </c>
+      <c r="U70" t="n">
+        <v>2025</v>
+      </c>
+      <c r="V70" t="n">
+        <v>64</v>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU (418457)</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>65</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>666502</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="G71" t="n">
+        <v>92.89</v>
+      </c>
+      <c r="H71" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="I71" t="n">
+        <v>100</v>
+      </c>
+      <c r="J71" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="K71" t="n">
+        <v>86.38</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="O71" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="P71" t="n">
+        <v>70.63</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>88.29000000000001</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>SEPTEMBER</t>
+        </is>
+      </c>
+      <c r="U71" t="n">
+        <v>2025</v>
+      </c>
+      <c r="V71" t="n">
+        <v>65</v>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>KEMENAG OKUT (666502)</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>66</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>424245</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>86.75</v>
+      </c>
+      <c r="G72" t="n">
+        <v>99.91</v>
+      </c>
+      <c r="H72" t="n">
+        <v>65</v>
+      </c>
+      <c r="I72" t="n">
+        <v>100</v>
+      </c>
+      <c r="J72" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="K72" t="n">
+        <v>100</v>
+      </c>
+      <c r="L72" t="n">
+        <v>100</v>
+      </c>
+      <c r="M72" t="n">
+        <v>100</v>
+      </c>
+      <c r="N72" t="n">
+        <v>99.65000000000001</v>
+      </c>
+      <c r="O72" t="n">
+        <v>65</v>
+      </c>
+      <c r="P72" t="n">
+        <v>87.23999999999999</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>87.23999999999999</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>SEPTEMBER</t>
+        </is>
+      </c>
+      <c r="U72" t="n">
+        <v>2025</v>
+      </c>
+      <c r="V72" t="n">
+        <v>66</v>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>MAN 1 OKU</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>MAN 1 OKU</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>MAN 1 OKU (424245)</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>67</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>418461</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>81.53</v>
+      </c>
+      <c r="G73" t="n">
+        <v>82.56</v>
+      </c>
+      <c r="H73" t="n">
+        <v>100</v>
+      </c>
+      <c r="I73" t="n">
+        <v>100</v>
+      </c>
+      <c r="J73" t="n">
+        <v>63.05</v>
+      </c>
+      <c r="K73" t="n">
+        <v>70.22</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="O73" t="n">
+        <v>100</v>
+      </c>
+      <c r="P73" t="n">
+        <v>67.98999999999999</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>84.98999999999999</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>SEPTEMBER</t>
+        </is>
+      </c>
+      <c r="U73" t="n">
+        <v>2025</v>
+      </c>
+      <c r="V73" t="n">
+        <v>67</v>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU (418461)</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
         <v>68</v>
       </c>
-      <c r="W69" t="inlineStr">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>691653</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>DINAS TENAGA KERJA DAN TRANSMIGRASI KABUPATEN OKU TIMUR</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="G74" t="n">
+        <v>46.99</v>
+      </c>
+      <c r="H74" t="n">
+        <v>100</v>
+      </c>
+      <c r="I74" t="n">
+        <v>100</v>
+      </c>
+      <c r="J74" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="K74" t="n">
+        <v>33.98</v>
+      </c>
+      <c r="L74" t="n">
+        <v>60</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>100</v>
+      </c>
+      <c r="P74" t="n">
+        <v>55.54</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>69.42</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>SEPTEMBER</t>
+        </is>
+      </c>
+      <c r="U74" t="n">
+        <v>2025</v>
+      </c>
+      <c r="V74" t="n">
+        <v>68</v>
+      </c>
+      <c r="W74" t="inlineStr">
         <is>
           <t>DISNAKERTRANS OKUT</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>DISNAKERTRANS OKUT</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Y74" t="inlineStr">
         <is>
           <t>DISNAKERTRANS OKUT (691653)</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>

--- a/data/IKPA_SEPTEMBER_2025.xlsx
+++ b/data/IKPA_SEPTEMBER_2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z74"/>
+  <dimension ref="A1:Z69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3162,7 +3162,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3171,24 +3171,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>'007130</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>90.34</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>99.89</v>
+        <v>100</v>
       </c>
       <c r="H28" t="n">
         <v>100</v>
@@ -3197,16 +3197,16 @@
         <v>100</v>
       </c>
       <c r="J28" t="n">
-        <v>80.68000000000001</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>99.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="L28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>100</v>
@@ -3215,18 +3215,18 @@
         <v>100</v>
       </c>
       <c r="P28" t="n">
-        <v>97.02</v>
+        <v>77.39</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>97.02</v>
+        <v>96.73</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3237,21 +3237,21 @@
         <v>2025</v>
       </c>
       <c r="V28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>KEJARI  OKU ('007130)</t>
+          <t>MTSN 2 OKUT (418471)</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -3262,7 +3262,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3271,24 +3271,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>'007190</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>91.29000000000001</v>
+        <v>88.95</v>
       </c>
       <c r="G29" t="n">
-        <v>100</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="H29" t="n">
         <v>100</v>
@@ -3297,36 +3297,36 @@
         <v>100</v>
       </c>
       <c r="J29" t="n">
-        <v>82.56999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K29" t="n">
         <v>100</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N29" t="n">
-        <v>100</v>
+        <v>99.83</v>
       </c>
       <c r="O29" t="n">
         <v>100</v>
       </c>
       <c r="P29" t="n">
-        <v>77.39</v>
+        <v>96.67</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>96.73</v>
+        <v>96.67</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3337,21 +3337,21 @@
         <v>2025</v>
       </c>
       <c r="V29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT (418471)</t>
+          <t>KEJARI OKUT ('007190)</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -3362,7 +3362,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3371,24 +3371,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>'007190</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>88.95</v>
+        <v>91.03</v>
       </c>
       <c r="G30" t="n">
-        <v>99.95999999999999</v>
+        <v>98.33</v>
       </c>
       <c r="H30" t="n">
         <v>100</v>
@@ -3397,25 +3397,25 @@
         <v>100</v>
       </c>
       <c r="J30" t="n">
-        <v>77.90000000000001</v>
+        <v>82.05</v>
       </c>
       <c r="K30" t="n">
         <v>100</v>
       </c>
       <c r="L30" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="M30" t="n">
         <v>100</v>
       </c>
       <c r="N30" t="n">
-        <v>99.83</v>
+        <v>100</v>
       </c>
       <c r="O30" t="n">
         <v>100</v>
       </c>
       <c r="P30" t="n">
-        <v>96.67</v>
+        <v>96.64</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>96.67</v>
+        <v>96.64</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3437,21 +3437,21 @@
         <v>2025</v>
       </c>
       <c r="V30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>KEJARI OKUT ('007190)</t>
+          <t>KPU OKUT (656560)</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -3462,7 +3462,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3471,24 +3471,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>'007190</t>
+          <t>666505</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>88.95</v>
+        <v>91.04000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>99.95999999999999</v>
+        <v>100</v>
       </c>
       <c r="H31" t="n">
         <v>100</v>
@@ -3497,36 +3497,36 @@
         <v>100</v>
       </c>
       <c r="J31" t="n">
-        <v>77.90000000000001</v>
+        <v>82.08</v>
       </c>
       <c r="K31" t="n">
         <v>100</v>
       </c>
       <c r="L31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>99.83</v>
+        <v>100</v>
       </c>
       <c r="O31" t="n">
         <v>100</v>
       </c>
       <c r="P31" t="n">
-        <v>96.67</v>
+        <v>77.31</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>96.67</v>
+        <v>96.64</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3537,21 +3537,21 @@
         <v>2025</v>
       </c>
       <c r="V31" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>KEJARI OKUT ('007190)</t>
+          <t>KEMENAG OKUT (666505)</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -3562,7 +3562,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -3571,24 +3571,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>'098963</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>91.03</v>
+        <v>88.64</v>
       </c>
       <c r="G32" t="n">
-        <v>98.33</v>
+        <v>100</v>
       </c>
       <c r="H32" t="n">
         <v>100</v>
@@ -3597,13 +3597,13 @@
         <v>100</v>
       </c>
       <c r="J32" t="n">
-        <v>82.05</v>
+        <v>77.27</v>
       </c>
       <c r="K32" t="n">
         <v>100</v>
       </c>
       <c r="L32" t="n">
-        <v>93.33</v>
+        <v>100</v>
       </c>
       <c r="M32" t="n">
         <v>100</v>
@@ -3615,7 +3615,7 @@
         <v>100</v>
       </c>
       <c r="P32" t="n">
-        <v>96.64</v>
+        <v>96.59</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>96.64</v>
+        <v>96.59</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3637,21 +3637,21 @@
         <v>2025</v>
       </c>
       <c r="V32" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>KPU OKUT (656560)</t>
+          <t>PN BATURAJA ('098963)</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -3662,7 +3662,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -3671,24 +3671,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>666505</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>91.04000000000001</v>
+        <v>88.41</v>
       </c>
       <c r="G33" t="n">
-        <v>100</v>
+        <v>99.86</v>
       </c>
       <c r="H33" t="n">
         <v>100</v>
@@ -3697,16 +3697,16 @@
         <v>100</v>
       </c>
       <c r="J33" t="n">
-        <v>82.08</v>
+        <v>76.81</v>
       </c>
       <c r="K33" t="n">
-        <v>100</v>
+        <v>99.45</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N33" t="n">
         <v>100</v>
@@ -3715,18 +3715,18 @@
         <v>100</v>
       </c>
       <c r="P33" t="n">
-        <v>77.31</v>
+        <v>96.41</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>96.64</v>
+        <v>96.41</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3737,21 +3737,21 @@
         <v>2025</v>
       </c>
       <c r="V33" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666505)</t>
+          <t>LAPAS MUARA DUA (692334)</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -3762,7 +3762,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -3771,24 +3771,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>'098963</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>88.64</v>
+        <v>94.77</v>
       </c>
       <c r="G34" t="n">
-        <v>100</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="H34" t="n">
         <v>100</v>
@@ -3797,25 +3797,25 @@
         <v>100</v>
       </c>
       <c r="J34" t="n">
-        <v>77.27</v>
+        <v>89.53</v>
       </c>
       <c r="K34" t="n">
         <v>100</v>
       </c>
       <c r="L34" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="M34" t="n">
         <v>100</v>
       </c>
       <c r="N34" t="n">
-        <v>100</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="O34" t="n">
         <v>100</v>
       </c>
       <c r="P34" t="n">
-        <v>96.59</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>96.59</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3837,21 +3837,21 @@
         <v>2025</v>
       </c>
       <c r="V34" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>PN BATURAJA ('098963)</t>
+          <t>KPU OKU (656553)</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -3862,7 +3862,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3871,24 +3871,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>'098963</t>
+          <t>418462</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>88.64</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>100</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
@@ -3897,36 +3897,36 @@
         <v>100</v>
       </c>
       <c r="J35" t="n">
-        <v>77.27</v>
+        <v>80.98</v>
       </c>
       <c r="K35" t="n">
-        <v>100</v>
+        <v>99.33</v>
       </c>
       <c r="L35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>100</v>
+        <v>99.69</v>
       </c>
       <c r="O35" t="n">
         <v>100</v>
       </c>
       <c r="P35" t="n">
-        <v>96.59</v>
+        <v>76.98</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>96.59</v>
+        <v>96.23</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3937,21 +3937,21 @@
         <v>2025</v>
       </c>
       <c r="V35" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>PN BATURAJA ('098963)</t>
+          <t>MTSN 2 OKUS (418462)</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -3962,7 +3962,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -3976,19 +3976,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>692340</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>LAPAS KELAS II B MARTAPURA</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>88.41</v>
+        <v>88.04000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>99.86</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="H36" t="n">
         <v>100</v>
@@ -3997,10 +3997,10 @@
         <v>100</v>
       </c>
       <c r="J36" t="n">
-        <v>76.81</v>
+        <v>76.08</v>
       </c>
       <c r="K36" t="n">
-        <v>99.45</v>
+        <v>99.05</v>
       </c>
       <c r="L36" t="n">
         <v>100</v>
@@ -4015,7 +4015,7 @@
         <v>100</v>
       </c>
       <c r="P36" t="n">
-        <v>96.41</v>
+        <v>96.22</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>96.41</v>
+        <v>96.22</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4037,21 +4037,21 @@
         <v>2025</v>
       </c>
       <c r="V36" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA (692334)</t>
+          <t>LAPAS MARTAPURA (692340)</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -4062,7 +4062,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4071,24 +4071,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>670561</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>94.77</v>
+        <v>86.95</v>
       </c>
       <c r="G37" t="n">
-        <v>94.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
@@ -4097,25 +4097,25 @@
         <v>100</v>
       </c>
       <c r="J37" t="n">
-        <v>89.53</v>
+        <v>73.89</v>
       </c>
       <c r="K37" t="n">
         <v>100</v>
       </c>
       <c r="L37" t="n">
-        <v>93.33</v>
+        <v>100</v>
       </c>
       <c r="M37" t="n">
         <v>100</v>
       </c>
       <c r="N37" t="n">
-        <v>84.95999999999999</v>
+        <v>100</v>
       </c>
       <c r="O37" t="n">
         <v>100</v>
       </c>
       <c r="P37" t="n">
-        <v>96.26000000000001</v>
+        <v>96.08</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>96.26000000000001</v>
+        <v>96.08</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4137,21 +4137,21 @@
         <v>2025</v>
       </c>
       <c r="V37" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>KPU OKU (656553)</t>
+          <t>BPN OKUS (670561)</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -4162,7 +4162,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4176,19 +4176,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>418462</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>90.48999999999999</v>
+        <v>96.06</v>
       </c>
       <c r="G38" t="n">
-        <v>99.51000000000001</v>
+        <v>93.34</v>
       </c>
       <c r="H38" t="n">
         <v>100</v>
@@ -4197,10 +4197,10 @@
         <v>100</v>
       </c>
       <c r="J38" t="n">
-        <v>80.98</v>
+        <v>92.11</v>
       </c>
       <c r="K38" t="n">
-        <v>99.33</v>
+        <v>93.03</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>99.69</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="O38" t="n">
         <v>100</v>
       </c>
       <c r="P38" t="n">
-        <v>76.98</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>96.23</v>
+        <v>95.98</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4237,21 +4237,21 @@
         <v>2025</v>
       </c>
       <c r="V38" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS (418462)</t>
+          <t>KEMENAG OKUT (666504)</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -4262,7 +4262,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4271,62 +4271,62 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>692340</t>
+          <t>661192</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MARTAPURA</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>88.04000000000001</v>
+        <v>90.94</v>
       </c>
       <c r="G39" t="n">
-        <v>99.76000000000001</v>
+        <v>99.92</v>
       </c>
       <c r="H39" t="n">
-        <v>100</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="I39" t="n">
         <v>100</v>
       </c>
       <c r="J39" t="n">
-        <v>76.08</v>
+        <v>81.88</v>
       </c>
       <c r="K39" t="n">
-        <v>99.05</v>
+        <v>100</v>
       </c>
       <c r="L39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>100</v>
+        <v>99.83</v>
       </c>
       <c r="O39" t="n">
-        <v>100</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="P39" t="n">
-        <v>96.22</v>
+        <v>76.66</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>96.22</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4337,21 +4337,21 @@
         <v>2025</v>
       </c>
       <c r="V39" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA (692340)</t>
+          <t>MTSN 4 OKUS (661192)</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -4362,7 +4362,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -4371,24 +4371,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>86.95</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H40" t="n">
         <v>100</v>
@@ -4397,36 +4397,36 @@
         <v>100</v>
       </c>
       <c r="J40" t="n">
-        <v>73.89</v>
+        <v>83.69</v>
       </c>
       <c r="K40" t="n">
-        <v>100</v>
+        <v>99.94</v>
       </c>
       <c r="L40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>100</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="O40" t="n">
         <v>100</v>
       </c>
       <c r="P40" t="n">
-        <v>96.08</v>
+        <v>76.55</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>96.08</v>
+        <v>95.69</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4437,21 +4437,21 @@
         <v>2025</v>
       </c>
       <c r="V40" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>BPN OKUS (670561)</t>
+          <t>KPU OKUS (656574)</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -4462,7 +4462,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -4476,31 +4476,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>666504</t>
+          <t>440503</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>96.06</v>
+        <v>96.94</v>
       </c>
       <c r="G41" t="n">
-        <v>93.34</v>
+        <v>96.44</v>
       </c>
       <c r="H41" t="n">
-        <v>100</v>
+        <v>95.56</v>
       </c>
       <c r="I41" t="n">
         <v>100</v>
       </c>
       <c r="J41" t="n">
-        <v>92.11</v>
+        <v>93.88</v>
       </c>
       <c r="K41" t="n">
-        <v>93.03</v>
+        <v>92.88</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -4509,13 +4509,13 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>93.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="O41" t="n">
-        <v>100</v>
+        <v>95.56</v>
       </c>
       <c r="P41" t="n">
-        <v>76.79000000000001</v>
+        <v>76.55</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>95.98</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4537,21 +4537,21 @@
         <v>2025</v>
       </c>
       <c r="V41" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666504)</t>
+          <t>KEMENAG OKUS (440503)</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
@@ -4562,7 +4562,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -4576,57 +4576,57 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>661192</t>
+          <t>424967</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>90.94</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>99.92</v>
+        <v>98.28</v>
       </c>
       <c r="H42" t="n">
-        <v>97.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="I42" t="n">
         <v>100</v>
       </c>
       <c r="J42" t="n">
-        <v>81.88</v>
+        <v>79.69</v>
       </c>
       <c r="K42" t="n">
-        <v>100</v>
+        <v>93.11</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N42" t="n">
-        <v>99.83</v>
+        <v>100</v>
       </c>
       <c r="O42" t="n">
-        <v>97.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="P42" t="n">
-        <v>76.66</v>
+        <v>95.58</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>95.81999999999999</v>
+        <v>95.58</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4637,21 +4637,21 @@
         <v>2025</v>
       </c>
       <c r="V42" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS (661192)</t>
+          <t>MTSN 1 OKUT (424967)</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
@@ -4662,7 +4662,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -4671,24 +4671,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>91.84999999999999</v>
+        <v>85.41</v>
       </c>
       <c r="G43" t="n">
-        <v>95</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="H43" t="n">
         <v>100</v>
@@ -4697,36 +4697,36 @@
         <v>100</v>
       </c>
       <c r="J43" t="n">
-        <v>83.69</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>99.94</v>
+        <v>100</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N43" t="n">
-        <v>90.06999999999999</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="O43" t="n">
         <v>100</v>
       </c>
       <c r="P43" t="n">
-        <v>76.55</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>95.69</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4737,21 +4737,21 @@
         <v>2025</v>
       </c>
       <c r="V43" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>KPU OKUS (656574)</t>
+          <t>BPN OKU (431142)</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
@@ -4762,7 +4762,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>440503</t>
+          <t>440502</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4785,22 +4785,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>96.94</v>
+        <v>89.34</v>
       </c>
       <c r="G44" t="n">
-        <v>96.44</v>
+        <v>97.22</v>
       </c>
       <c r="H44" t="n">
-        <v>95.56</v>
+        <v>100</v>
       </c>
       <c r="I44" t="n">
         <v>100</v>
       </c>
       <c r="J44" t="n">
-        <v>93.88</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>92.88</v>
+        <v>100</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -4809,13 +4809,13 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>100</v>
+        <v>94.44</v>
       </c>
       <c r="O44" t="n">
-        <v>95.56</v>
+        <v>100</v>
       </c>
       <c r="P44" t="n">
-        <v>76.55</v>
+        <v>76.25</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>95.68000000000001</v>
+        <v>95.31</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>2025</v>
       </c>
       <c r="V44" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440503)</t>
+          <t>KEMENAG OKUS (440502)</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
@@ -4862,7 +4862,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -4876,19 +4876,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>426050</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>89.84999999999999</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>98.28</v>
+        <v>97.86</v>
       </c>
       <c r="H45" t="n">
         <v>100</v>
@@ -4897,36 +4897,36 @@
         <v>100</v>
       </c>
       <c r="J45" t="n">
-        <v>79.69</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>93.11</v>
+        <v>100</v>
       </c>
       <c r="L45" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>100</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="O45" t="n">
         <v>100</v>
       </c>
       <c r="P45" t="n">
-        <v>95.58</v>
+        <v>75.97</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>95.58</v>
+        <v>94.97</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4937,21 +4937,21 @@
         <v>2025</v>
       </c>
       <c r="V45" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT (424967)</t>
+          <t>MTSN 1 OKU (426050)</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
@@ -4962,7 +4962,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -4971,24 +4971,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>692725</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+          <t>RUPBASAN KELAS II BATURAJA</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>85.41</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>99.68000000000001</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="H46" t="n">
         <v>100</v>
@@ -4997,10 +4997,10 @@
         <v>100</v>
       </c>
       <c r="J46" t="n">
-        <v>70.81999999999999</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>100</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="L46" t="n">
         <v>100</v>
@@ -5009,13 +5009,13 @@
         <v>100</v>
       </c>
       <c r="N46" t="n">
-        <v>98.70999999999999</v>
+        <v>92.86</v>
       </c>
       <c r="O46" t="n">
         <v>100</v>
       </c>
       <c r="P46" t="n">
-        <v>95.48999999999999</v>
+        <v>94.94</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>95.48999999999999</v>
+        <v>94.94</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5037,21 +5037,21 @@
         <v>2025</v>
       </c>
       <c r="V46" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>RUPBASAN BATURAJA</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>RUPBASAN BATURAJA</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>BPN OKU (431142)</t>
+          <t>RUPBASAN BATURAJA (692725)</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
@@ -5062,7 +5062,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -5076,19 +5076,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>440502</t>
+          <t>597558</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>89.34</v>
+        <v>87.89</v>
       </c>
       <c r="G47" t="n">
-        <v>97.22</v>
+        <v>97.77</v>
       </c>
       <c r="H47" t="n">
         <v>100</v>
@@ -5097,7 +5097,7 @@
         <v>100</v>
       </c>
       <c r="J47" t="n">
-        <v>78.68000000000001</v>
+        <v>75.77</v>
       </c>
       <c r="K47" t="n">
         <v>100</v>
@@ -5109,13 +5109,13 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>94.44</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="O47" t="n">
         <v>100</v>
       </c>
       <c r="P47" t="n">
-        <v>76.25</v>
+        <v>75.92</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>95.31</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5137,21 +5137,21 @@
         <v>2025</v>
       </c>
       <c r="V47" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440502)</t>
+          <t>MAN 2 OKUS (597558)</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
@@ -5162,7 +5162,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -5176,28 +5176,28 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>662127</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>88.01000000000001</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>97.86</v>
+        <v>100</v>
       </c>
       <c r="H48" t="n">
-        <v>100</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="I48" t="n">
         <v>100</v>
       </c>
       <c r="J48" t="n">
-        <v>76.01000000000001</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="K48" t="n">
         <v>100</v>
@@ -5209,13 +5209,13 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>95.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="O48" t="n">
-        <v>100</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="P48" t="n">
-        <v>75.97</v>
+        <v>75.87</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>94.97</v>
+        <v>94.84</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5237,21 +5237,21 @@
         <v>2025</v>
       </c>
       <c r="V48" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU (426050)</t>
+          <t>MAN 1 OKUS (662127)</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -5262,7 +5262,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -5271,24 +5271,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>692725</t>
+          <t>426066</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RUPBASAN KELAS II BATURAJA</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>87.90000000000001</v>
+        <v>87.55</v>
       </c>
       <c r="G49" t="n">
-        <v>97.31999999999999</v>
+        <v>97.56</v>
       </c>
       <c r="H49" t="n">
         <v>100</v>
@@ -5297,25 +5297,25 @@
         <v>100</v>
       </c>
       <c r="J49" t="n">
-        <v>75.79000000000001</v>
+        <v>75.09</v>
       </c>
       <c r="K49" t="n">
-        <v>96.43000000000001</v>
+        <v>94.88</v>
       </c>
       <c r="L49" t="n">
-        <v>100</v>
+        <v>95.55</v>
       </c>
       <c r="M49" t="n">
         <v>100</v>
       </c>
       <c r="N49" t="n">
-        <v>92.86</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="O49" t="n">
         <v>100</v>
       </c>
       <c r="P49" t="n">
-        <v>94.94</v>
+        <v>94.77</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>94.94</v>
+        <v>94.77</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5337,21 +5337,21 @@
         <v>2025</v>
       </c>
       <c r="V49" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>RUPBASAN BATURAJA</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>RUPBASAN BATURAJA</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>RUPBASAN BATURAJA (692725)</t>
+          <t>MAN 1 OKUT (426066)</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
@@ -5362,7 +5362,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -5376,19 +5376,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>597558</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>87.89</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>97.77</v>
+        <v>100</v>
       </c>
       <c r="H50" t="n">
         <v>100</v>
@@ -5397,7 +5397,7 @@
         <v>100</v>
       </c>
       <c r="J50" t="n">
-        <v>75.77</v>
+        <v>71.14</v>
       </c>
       <c r="K50" t="n">
         <v>100</v>
@@ -5409,13 +5409,13 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>95.54000000000001</v>
+        <v>100</v>
       </c>
       <c r="O50" t="n">
         <v>100</v>
       </c>
       <c r="P50" t="n">
-        <v>75.92</v>
+        <v>75.67</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>94.90000000000001</v>
+        <v>94.59</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5437,21 +5437,21 @@
         <v>2025</v>
       </c>
       <c r="V50" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS (597558)</t>
+          <t>KEMENAG OKU (418459)</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
@@ -5462,7 +5462,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -5476,31 +5476,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>662127</t>
+          <t>553792</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>91.01000000000001</v>
+        <v>90.42</v>
       </c>
       <c r="G51" t="n">
-        <v>100</v>
+        <v>96.25</v>
       </c>
       <c r="H51" t="n">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="I51" t="n">
         <v>100</v>
       </c>
       <c r="J51" t="n">
-        <v>82.01000000000001</v>
+        <v>80.83</v>
       </c>
       <c r="K51" t="n">
-        <v>100</v>
+        <v>92.48999999999999</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -5512,10 +5512,10 @@
         <v>100</v>
       </c>
       <c r="O51" t="n">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="P51" t="n">
-        <v>75.87</v>
+        <v>75.62</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>94.84</v>
+        <v>94.53</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5537,21 +5537,21 @@
         <v>2025</v>
       </c>
       <c r="V51" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS (662127)</t>
+          <t>MTSN 1 OKUS (553792)</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
@@ -5562,7 +5562,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -5576,19 +5576,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>87.55</v>
+        <v>87.17</v>
       </c>
       <c r="G52" t="n">
-        <v>97.56</v>
+        <v>98.23999999999999</v>
       </c>
       <c r="H52" t="n">
         <v>100</v>
@@ -5597,36 +5597,36 @@
         <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>75.09</v>
+        <v>74.33</v>
       </c>
       <c r="K52" t="n">
-        <v>94.88</v>
+        <v>96.47</v>
       </c>
       <c r="L52" t="n">
-        <v>95.55</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>99.79000000000001</v>
+        <v>100</v>
       </c>
       <c r="O52" t="n">
         <v>100</v>
       </c>
       <c r="P52" t="n">
-        <v>94.77</v>
+        <v>75.44</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>94.77</v>
+        <v>94.3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5637,21 +5637,21 @@
         <v>2025</v>
       </c>
       <c r="V52" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT (426066)</t>
+          <t>KEMENAG OKUT (666503)</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
@@ -5662,7 +5662,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -5671,62 +5671,62 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>'007208</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>85.56999999999999</v>
+        <v>88.88</v>
       </c>
       <c r="G53" t="n">
         <v>100</v>
       </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>90.56</v>
       </c>
       <c r="I53" t="n">
         <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>71.14</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="K53" t="n">
         <v>100</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N53" t="n">
         <v>100</v>
       </c>
       <c r="O53" t="n">
-        <v>100</v>
+        <v>90.56</v>
       </c>
       <c r="P53" t="n">
-        <v>75.67</v>
+        <v>94.3</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>94.59</v>
+        <v>94.3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5737,21 +5737,21 @@
         <v>2025</v>
       </c>
       <c r="V53" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEJARI  OKUS</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEJARI  OKUS</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418459)</t>
+          <t>KEJARI  OKUS ('007208)</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
@@ -5762,7 +5762,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -5776,19 +5776,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>90.42</v>
+        <v>89.75</v>
       </c>
       <c r="G54" t="n">
-        <v>96.25</v>
+        <v>95.02</v>
       </c>
       <c r="H54" t="n">
         <v>100</v>
@@ -5797,10 +5797,10 @@
         <v>100</v>
       </c>
       <c r="J54" t="n">
-        <v>80.83</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>92.48999999999999</v>
+        <v>94.84</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -5809,13 +5809,13 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="O54" t="n">
         <v>100</v>
       </c>
       <c r="P54" t="n">
-        <v>75.62</v>
+        <v>75.41</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>94.53</v>
+        <v>94.26000000000001</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5837,21 +5837,21 @@
         <v>2025</v>
       </c>
       <c r="V54" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS (553792)</t>
+          <t>KEMENAG OKU (418458)</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
@@ -5862,7 +5862,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -5871,62 +5871,62 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>344894</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>87.17</v>
+        <v>84.92</v>
       </c>
       <c r="G55" t="n">
-        <v>98.23999999999999</v>
+        <v>99.25</v>
       </c>
       <c r="H55" t="n">
-        <v>100</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="I55" t="n">
         <v>100</v>
       </c>
       <c r="J55" t="n">
-        <v>74.33</v>
+        <v>69.84</v>
       </c>
       <c r="K55" t="n">
-        <v>96.47</v>
+        <v>98.58</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N55" t="n">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O55" t="n">
-        <v>100</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="P55" t="n">
-        <v>75.44</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>94.3</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5937,21 +5937,21 @@
         <v>2025</v>
       </c>
       <c r="V55" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666503)</t>
+          <t>RUMKIT NOESMIR (344894)</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
@@ -5962,7 +5962,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -5971,62 +5971,62 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>066</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>'007208</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>88.88</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>100</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>90.56</v>
+        <v>100</v>
       </c>
       <c r="I56" t="n">
         <v>100</v>
       </c>
       <c r="J56" t="n">
-        <v>77.76000000000001</v>
+        <v>69.98</v>
       </c>
       <c r="K56" t="n">
         <v>100</v>
       </c>
       <c r="L56" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>100</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="O56" t="n">
-        <v>90.56</v>
+        <v>100</v>
       </c>
       <c r="P56" t="n">
-        <v>94.3</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>94.3</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6037,21 +6037,21 @@
         <v>2025</v>
       </c>
       <c r="V56" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>KEJARI  OKUS</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>KEJARI  OKUS</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>KEJARI  OKUS ('007208)</t>
+          <t>BNN OKUT (111079)</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
@@ -6062,7 +6062,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -6071,36 +6071,36 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>024</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>'007208</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>88.88</v>
+        <v>88.73</v>
       </c>
       <c r="G57" t="n">
-        <v>100</v>
+        <v>96.87</v>
       </c>
       <c r="H57" t="n">
-        <v>90.56</v>
+        <v>98.09</v>
       </c>
       <c r="I57" t="n">
         <v>100</v>
       </c>
       <c r="J57" t="n">
-        <v>77.76000000000001</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="K57" t="n">
-        <v>100</v>
+        <v>91.69</v>
       </c>
       <c r="L57" t="n">
         <v>100</v>
@@ -6109,13 +6109,13 @@
         <v>100</v>
       </c>
       <c r="N57" t="n">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="O57" t="n">
-        <v>90.56</v>
+        <v>98.09</v>
       </c>
       <c r="P57" t="n">
-        <v>94.3</v>
+        <v>94.06</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>94.3</v>
+        <v>94.06</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6137,21 +6137,21 @@
         <v>2025</v>
       </c>
       <c r="V57" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>KEJARI  OKUS</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>KEJARI  OKUS</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>KEJARI  OKUS ('007208)</t>
+          <t>LOKA LABKESMAS (690801)</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
@@ -6162,7 +6162,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -6176,31 +6176,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>418458</t>
+          <t>666501</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>89.75</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>95.02</v>
+        <v>92.01000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I58" t="n">
         <v>100</v>
       </c>
       <c r="J58" t="n">
-        <v>79.48999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="K58" t="n">
-        <v>94.84</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -6209,13 +6209,13 @@
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>95.2</v>
+        <v>84.03</v>
       </c>
       <c r="O58" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P58" t="n">
-        <v>75.41</v>
+        <v>74.66</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>94.26000000000001</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6237,21 +6237,21 @@
         <v>2025</v>
       </c>
       <c r="V58" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418458)</t>
+          <t>KEMENAG OKUT (666501)</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
@@ -6262,7 +6262,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -6271,36 +6271,36 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>419006</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>84.92</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>99.25</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>96.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="I59" t="n">
         <v>100</v>
       </c>
       <c r="J59" t="n">
-        <v>69.84</v>
+        <v>68.52</v>
       </c>
       <c r="K59" t="n">
-        <v>98.58</v>
+        <v>100</v>
       </c>
       <c r="L59" t="n">
         <v>100</v>
@@ -6309,13 +6309,13 @@
         <v>100</v>
       </c>
       <c r="N59" t="n">
-        <v>98.40000000000001</v>
+        <v>79.02</v>
       </c>
       <c r="O59" t="n">
-        <v>96.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="P59" t="n">
-        <v>94.20999999999999</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>94.20999999999999</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6337,21 +6337,21 @@
         <v>2025</v>
       </c>
       <c r="V59" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR (344894)</t>
+          <t>BAWASLU OKU (419006)</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
@@ -6362,7 +6362,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -6371,33 +6371,33 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>686503</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>84.98999999999999</v>
+        <v>86.14</v>
       </c>
       <c r="G60" t="n">
-        <v>99.23999999999999</v>
+        <v>97.13</v>
       </c>
       <c r="H60" t="n">
-        <v>100</v>
+        <v>95.63</v>
       </c>
       <c r="I60" t="n">
         <v>100</v>
       </c>
       <c r="J60" t="n">
-        <v>69.98</v>
+        <v>72.27</v>
       </c>
       <c r="K60" t="n">
         <v>100</v>
@@ -6409,13 +6409,13 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>98.48999999999999</v>
+        <v>94.26000000000001</v>
       </c>
       <c r="O60" t="n">
-        <v>100</v>
+        <v>95.63</v>
       </c>
       <c r="P60" t="n">
-        <v>75.34999999999999</v>
+        <v>74.17</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>94.18000000000001</v>
+        <v>92.72</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6437,21 +6437,21 @@
         <v>2025</v>
       </c>
       <c r="V60" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>BNN OKUT (111079)</t>
+          <t>BAWASLU OKUS (686503)</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
@@ -6462,7 +6462,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -6471,36 +6471,36 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>403410</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>88.73</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="G61" t="n">
-        <v>96.87</v>
+        <v>98.63</v>
       </c>
       <c r="H61" t="n">
-        <v>98.09</v>
+        <v>76.67</v>
       </c>
       <c r="I61" t="n">
         <v>100</v>
       </c>
       <c r="J61" t="n">
-        <v>77.45999999999999</v>
+        <v>91.36</v>
       </c>
       <c r="K61" t="n">
-        <v>91.69</v>
+        <v>97.59</v>
       </c>
       <c r="L61" t="n">
         <v>100</v>
@@ -6509,13 +6509,13 @@
         <v>100</v>
       </c>
       <c r="N61" t="n">
-        <v>95.8</v>
+        <v>96.92</v>
       </c>
       <c r="O61" t="n">
-        <v>98.09</v>
+        <v>76.67</v>
       </c>
       <c r="P61" t="n">
-        <v>94.06</v>
+        <v>92.08</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>94.06</v>
+        <v>92.08</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6537,21 +6537,21 @@
         <v>2025</v>
       </c>
       <c r="V61" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS (690801)</t>
+          <t>PA  MUARADUA (403410)</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
@@ -6562,7 +6562,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -6576,31 +6576,31 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>666501</t>
+          <t>574370</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>93.34999999999999</v>
+        <v>84.55</v>
       </c>
       <c r="G62" t="n">
-        <v>92.01000000000001</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="I62" t="n">
         <v>100</v>
       </c>
       <c r="J62" t="n">
-        <v>86.7</v>
+        <v>69.09</v>
       </c>
       <c r="K62" t="n">
-        <v>99.98999999999999</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -6609,13 +6609,13 @@
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>84.03</v>
+        <v>88.56</v>
       </c>
       <c r="O62" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="P62" t="n">
-        <v>74.66</v>
+        <v>73.22</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>93.31999999999999</v>
+        <v>91.53</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6637,21 +6637,21 @@
         <v>2025</v>
       </c>
       <c r="V62" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666501)</t>
+          <t>MTSN 3 OKUS (574370)</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
@@ -6662,7 +6662,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -6671,24 +6671,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>666507</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>84.26000000000001</v>
+        <v>88.03</v>
       </c>
       <c r="G63" t="n">
-        <v>94.76000000000001</v>
+        <v>83.22</v>
       </c>
       <c r="H63" t="n">
         <v>100</v>
@@ -6697,36 +6697,36 @@
         <v>100</v>
       </c>
       <c r="J63" t="n">
-        <v>68.52</v>
+        <v>76.05</v>
       </c>
       <c r="K63" t="n">
-        <v>100</v>
+        <v>86.67</v>
       </c>
       <c r="L63" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>79.02</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="O63" t="n">
         <v>100</v>
       </c>
       <c r="P63" t="n">
-        <v>93.18000000000001</v>
+        <v>71.72</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>93.18000000000001</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6737,21 +6737,21 @@
         <v>2025</v>
       </c>
       <c r="V63" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>BAWASLU OKU (419006)</t>
+          <t>KEMENAG OKUT (666507)</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
@@ -6762,7 +6762,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -6771,36 +6771,36 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>686503</t>
+          <t>'099228</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>86.14</v>
+        <v>87.06</v>
       </c>
       <c r="G64" t="n">
-        <v>97.13</v>
+        <v>92.23</v>
       </c>
       <c r="H64" t="n">
-        <v>95.63</v>
+        <v>91.92</v>
       </c>
       <c r="I64" t="n">
         <v>100</v>
       </c>
       <c r="J64" t="n">
-        <v>72.27</v>
+        <v>74.12</v>
       </c>
       <c r="K64" t="n">
-        <v>100</v>
+        <v>88.17</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -6809,13 +6809,13 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>94.26000000000001</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="O64" t="n">
-        <v>95.63</v>
+        <v>91.92</v>
       </c>
       <c r="P64" t="n">
-        <v>74.17</v>
+        <v>71.36</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -6826,7 +6826,7 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>92.72</v>
+        <v>89.2</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6837,21 +6837,21 @@
         <v>2025</v>
       </c>
       <c r="V64" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS (686503)</t>
+          <t>PN BATURAJA ('099228)</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
@@ -6862,7 +6862,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -6871,62 +6871,62 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>403410</t>
+          <t>418457</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>95.68000000000001</v>
+        <v>85.58</v>
       </c>
       <c r="G65" t="n">
-        <v>98.63</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="H65" t="n">
-        <v>76.67</v>
+        <v>100</v>
       </c>
       <c r="I65" t="n">
         <v>100</v>
       </c>
       <c r="J65" t="n">
-        <v>91.36</v>
+        <v>71.16</v>
       </c>
       <c r="K65" t="n">
-        <v>97.59</v>
+        <v>83.37</v>
       </c>
       <c r="L65" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>96.92</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="O65" t="n">
-        <v>76.67</v>
+        <v>100</v>
       </c>
       <c r="P65" t="n">
-        <v>92.08</v>
+        <v>70.91</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>92.08</v>
+        <v>88.64</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6937,21 +6937,21 @@
         <v>2025</v>
       </c>
       <c r="V65" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>PA  MUARADUA (403410)</t>
+          <t>KEMENAG OKU (418457)</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
@@ -6962,7 +6962,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -6976,31 +6976,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>666502</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>84.55</v>
+        <v>84.8</v>
       </c>
       <c r="G66" t="n">
-        <v>91.79000000000001</v>
+        <v>92.89</v>
       </c>
       <c r="H66" t="n">
-        <v>100</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I66" t="n">
         <v>100</v>
       </c>
       <c r="J66" t="n">
-        <v>69.09</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>95.01000000000001</v>
+        <v>86.38</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -7009,13 +7009,13 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>88.56</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="O66" t="n">
-        <v>100</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="P66" t="n">
-        <v>73.22</v>
+        <v>70.63</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>91.53</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7037,21 +7037,21 @@
         <v>2025</v>
       </c>
       <c r="V66" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS (574370)</t>
+          <t>KEMENAG OKUT (666502)</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
@@ -7062,7 +7062,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -7076,57 +7076,57 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>666507</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>88.03</v>
+        <v>86.75</v>
       </c>
       <c r="G67" t="n">
-        <v>83.22</v>
+        <v>99.91</v>
       </c>
       <c r="H67" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="I67" t="n">
         <v>100</v>
       </c>
       <c r="J67" t="n">
-        <v>76.05</v>
+        <v>73.5</v>
       </c>
       <c r="K67" t="n">
-        <v>86.67</v>
+        <v>100</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N67" t="n">
-        <v>79.76000000000001</v>
+        <v>99.65000000000001</v>
       </c>
       <c r="O67" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="P67" t="n">
-        <v>71.72</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>89.65000000000001</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7137,21 +7137,21 @@
         <v>2025</v>
       </c>
       <c r="V67" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666507)</t>
+          <t>MAN 1 OKU (424245)</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
@@ -7162,7 +7162,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -7171,36 +7171,36 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>'099228</t>
+          <t>418461</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>87.06</v>
+        <v>81.53</v>
       </c>
       <c r="G68" t="n">
-        <v>92.23</v>
+        <v>82.56</v>
       </c>
       <c r="H68" t="n">
-        <v>91.92</v>
+        <v>100</v>
       </c>
       <c r="I68" t="n">
         <v>100</v>
       </c>
       <c r="J68" t="n">
-        <v>74.12</v>
+        <v>63.05</v>
       </c>
       <c r="K68" t="n">
-        <v>88.17</v>
+        <v>70.22</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -7209,13 +7209,13 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>96.29000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="O68" t="n">
-        <v>91.92</v>
+        <v>100</v>
       </c>
       <c r="P68" t="n">
-        <v>71.36</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>89.2</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7237,21 +7237,21 @@
         <v>2025</v>
       </c>
       <c r="V68" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>PN BATURAJA ('099228)</t>
+          <t>KEMENAG OKU (418461)</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
@@ -7262,7 +7262,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -7271,51 +7271,51 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>152</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>'099228</t>
+          <t>691653</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>DINAS TENAGA KERJA DAN TRANSMIGRASI KABUPATEN OKU TIMUR</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>87.06</v>
+        <v>75.8</v>
       </c>
       <c r="G69" t="n">
-        <v>92.23</v>
+        <v>46.99</v>
       </c>
       <c r="H69" t="n">
-        <v>91.92</v>
+        <v>100</v>
       </c>
       <c r="I69" t="n">
         <v>100</v>
       </c>
       <c r="J69" t="n">
-        <v>74.12</v>
+        <v>51.6</v>
       </c>
       <c r="K69" t="n">
-        <v>88.17</v>
+        <v>33.98</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>96.29000000000001</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>91.92</v>
+        <v>100</v>
       </c>
       <c r="P69" t="n">
-        <v>71.36</v>
+        <v>55.54</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>89.2</v>
+        <v>69.42</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7337,524 +7337,24 @@
         <v>2025</v>
       </c>
       <c r="V69" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>DISNAKERTRANS OKUT</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>DISNAKERTRANS OKUT</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>PN BATURAJA ('099228)</t>
+          <t>DISNAKERTRANS OKUT (691653)</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
-        <is>
-          <t>Upload</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>64</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>025</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>418457</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>85.58</v>
-      </c>
-      <c r="G70" t="n">
-        <v>84.51000000000001</v>
-      </c>
-      <c r="H70" t="n">
-        <v>100</v>
-      </c>
-      <c r="I70" t="n">
-        <v>100</v>
-      </c>
-      <c r="J70" t="n">
-        <v>71.16</v>
-      </c>
-      <c r="K70" t="n">
-        <v>83.37</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="n">
-        <v>85.65000000000001</v>
-      </c>
-      <c r="O70" t="n">
-        <v>100</v>
-      </c>
-      <c r="P70" t="n">
-        <v>70.91</v>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" t="n">
-        <v>88.64</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>SEPTEMBER</t>
-        </is>
-      </c>
-      <c r="U70" t="n">
-        <v>2025</v>
-      </c>
-      <c r="V70" t="n">
-        <v>64</v>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>KEMENAG OKU</t>
-        </is>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>KEMENAG OKU</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>KEMENAG OKU (418457)</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>Upload</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>65</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>025</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>666502</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="G71" t="n">
-        <v>92.89</v>
-      </c>
-      <c r="H71" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="I71" t="n">
-        <v>100</v>
-      </c>
-      <c r="J71" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="K71" t="n">
-        <v>86.38</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="O71" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="P71" t="n">
-        <v>70.63</v>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="n">
-        <v>88.29000000000001</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>SEPTEMBER</t>
-        </is>
-      </c>
-      <c r="U71" t="n">
-        <v>2025</v>
-      </c>
-      <c r="V71" t="n">
-        <v>65</v>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUT</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUT</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUT (666502)</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>Upload</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>66</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>025</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>424245</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>86.75</v>
-      </c>
-      <c r="G72" t="n">
-        <v>99.91</v>
-      </c>
-      <c r="H72" t="n">
-        <v>65</v>
-      </c>
-      <c r="I72" t="n">
-        <v>100</v>
-      </c>
-      <c r="J72" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="K72" t="n">
-        <v>100</v>
-      </c>
-      <c r="L72" t="n">
-        <v>100</v>
-      </c>
-      <c r="M72" t="n">
-        <v>100</v>
-      </c>
-      <c r="N72" t="n">
-        <v>99.65000000000001</v>
-      </c>
-      <c r="O72" t="n">
-        <v>65</v>
-      </c>
-      <c r="P72" t="n">
-        <v>87.23999999999999</v>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="n">
-        <v>87.23999999999999</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>SEPTEMBER</t>
-        </is>
-      </c>
-      <c r="U72" t="n">
-        <v>2025</v>
-      </c>
-      <c r="V72" t="n">
-        <v>66</v>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>MAN 1 OKU</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>MAN 1 OKU</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>MAN 1 OKU (424245)</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>Upload</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>67</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>025</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>418461</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>81.53</v>
-      </c>
-      <c r="G73" t="n">
-        <v>82.56</v>
-      </c>
-      <c r="H73" t="n">
-        <v>100</v>
-      </c>
-      <c r="I73" t="n">
-        <v>100</v>
-      </c>
-      <c r="J73" t="n">
-        <v>63.05</v>
-      </c>
-      <c r="K73" t="n">
-        <v>70.22</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="n">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="O73" t="n">
-        <v>100</v>
-      </c>
-      <c r="P73" t="n">
-        <v>67.98999999999999</v>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="n">
-        <v>84.98999999999999</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>SEPTEMBER</t>
-        </is>
-      </c>
-      <c r="U73" t="n">
-        <v>2025</v>
-      </c>
-      <c r="V73" t="n">
-        <v>67</v>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>KEMENAG OKU</t>
-        </is>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>KEMENAG OKU</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>KEMENAG OKU (418461)</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>Upload</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>68</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>691653</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>DINAS TENAGA KERJA DAN TRANSMIGRASI KABUPATEN OKU TIMUR</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="G74" t="n">
-        <v>46.99</v>
-      </c>
-      <c r="H74" t="n">
-        <v>100</v>
-      </c>
-      <c r="I74" t="n">
-        <v>100</v>
-      </c>
-      <c r="J74" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="K74" t="n">
-        <v>33.98</v>
-      </c>
-      <c r="L74" t="n">
-        <v>60</v>
-      </c>
-      <c r="M74" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" t="n">
-        <v>100</v>
-      </c>
-      <c r="P74" t="n">
-        <v>55.54</v>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="R74" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" t="n">
-        <v>69.42</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>SEPTEMBER</t>
-        </is>
-      </c>
-      <c r="U74" t="n">
-        <v>2025</v>
-      </c>
-      <c r="V74" t="n">
-        <v>68</v>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>DISNAKERTRANS OKUT</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>DISNAKERTRANS OKUT</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>DISNAKERTRANS OKUT (691653)</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>

--- a/data/IKPA_SEPTEMBER_2025.xlsx
+++ b/data/IKPA_SEPTEMBER_2025.xlsx
@@ -3041,17 +3041,17 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD (685001)</t>
+          <t>PUSLATPUR AD (685001)</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">

--- a/data/IKPA_SEPTEMBER_2025.xlsx
+++ b/data/IKPA_SEPTEMBER_2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z69"/>
+  <dimension ref="A1:Y69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,20 +541,15 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Uraian Satker-SINGKAT</t>
+          <t>Uraian Satker Final</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Uraian Satker Final</t>
+          <t>Satker</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Satker</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -646,15 +641,10 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>PA MARTAPURA (401944)</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
-        <is>
-          <t>PA MARTAPURA (401944)</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -746,15 +736,10 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>PA MARTAPURA (403409)</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
-        <is>
-          <t>PA MARTAPURA (403409)</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -846,15 +831,10 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>PA MUARADUA (401945)</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
-        <is>
-          <t>PA MUARADUA (401945)</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -946,15 +926,10 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>RUTAN BATURAJA (692339)</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
-        <is>
-          <t>RUTAN BATURAJA (692339)</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1046,15 +1021,10 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>PA BATURAJA (402268)</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
-        <is>
-          <t>PA BATURAJA (402268)</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1146,15 +1116,10 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>PA BATURAJA (402267)</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
-        <is>
-          <t>PA BATURAJA (402267)</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1246,15 +1211,10 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>KPP BATURAJA (410574)</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
-        <is>
-          <t>KPP BATURAJA (410574)</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1346,15 +1306,10 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>BPS OKU (428258)</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
-        <is>
-          <t>BPS OKU (428258)</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1446,15 +1401,10 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUS (440507)</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUS (440507)</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1546,15 +1496,10 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>KPPN BATURAJA (527975)</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
-        <is>
-          <t>KPPN BATURAJA (527975)</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1646,15 +1591,10 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUS (440505)</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUS (440505)</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1746,15 +1686,10 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>BPS OKUT (668529)</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
-        <is>
-          <t>BPS OKUT (668529)</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1846,15 +1781,10 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>POLRES OKUS</t>
+          <t>POLRES OKUS (665307)</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
-        <is>
-          <t>POLRES OKUS (665307)</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1946,15 +1876,10 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>BPS OKUS (667215)</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
-        <is>
-          <t>BPS OKUS (667215)</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2046,15 +1971,10 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>POLRES OKU (641681)</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
-        <is>
-          <t>POLRES OKU (641681)</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2146,15 +2066,10 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>BAPAS OKU INDUK (692625)</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
-        <is>
-          <t>BAPAS OKU INDUK (692625)</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2246,15 +2161,10 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUS (440506)</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUS (440506)</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2346,15 +2256,10 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>MTSN 4 OKUT (597480)</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
-        <is>
-          <t>MTSN 4 OKUT (597480)</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2446,15 +2351,10 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUS (440504)</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUS (440504)</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2546,15 +2446,10 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>MTSN 3 OKUT (553099)</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
-        <is>
-          <t>MTSN 3 OKUT (553099)</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2646,15 +2541,10 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUT (111071)</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUT (111071)</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2746,15 +2636,10 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKU (418456)</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
-        <is>
-          <t>KEMENAG OKU (418456)</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2846,15 +2731,10 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>POLRES OKUT (665292)</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
-        <is>
-          <t>POLRES OKUT (665292)</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2946,15 +2826,10 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>BPN OKUT (669055)</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
-        <is>
-          <t>BPN OKUT (669055)</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3046,15 +2921,10 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>PUSLATPUR AD (685001)</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
-        <is>
-          <t>PUSLATPUR AD (685001)</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3146,15 +3016,10 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>KEJARI  OKU ('007130)</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
-        <is>
-          <t>KEJARI  OKU ('007130)</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3246,15 +3111,10 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>MTSN 2 OKUT (418471)</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
-        <is>
-          <t>MTSN 2 OKUT (418471)</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3346,15 +3206,10 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>KEJARI OKUT ('007190)</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
-        <is>
-          <t>KEJARI OKUT ('007190)</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3446,15 +3301,10 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>KPU OKUT (656560)</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
-        <is>
-          <t>KPU OKUT (656560)</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3546,15 +3396,10 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUT (666505)</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUT (666505)</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3646,15 +3491,10 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>PN BATURAJA ('098963)</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
-        <is>
-          <t>PN BATURAJA ('098963)</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3746,15 +3586,10 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>LAPAS MUARA DUA (692334)</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
-        <is>
-          <t>LAPAS MUARA DUA (692334)</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3846,15 +3681,10 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>KPU OKU (656553)</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
-        <is>
-          <t>KPU OKU (656553)</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3946,15 +3776,10 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>MTSN 2 OKUS (418462)</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
-        <is>
-          <t>MTSN 2 OKUS (418462)</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4046,15 +3871,10 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>LAPAS MARTAPURA (692340)</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
-        <is>
-          <t>LAPAS MARTAPURA (692340)</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4146,15 +3966,10 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>BPN OKUS (670561)</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
-        <is>
-          <t>BPN OKUS (670561)</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4246,15 +4061,10 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUT (666504)</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUT (666504)</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4346,15 +4156,10 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>MTSN 4 OKUS (661192)</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
-        <is>
-          <t>MTSN 4 OKUS (661192)</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4446,15 +4251,10 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>KPU OKUS (656574)</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
-        <is>
-          <t>KPU OKUS (656574)</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4546,15 +4346,10 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUS (440503)</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUS (440503)</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4646,15 +4441,10 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>MTSN 1 OKUT (424967)</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
-        <is>
-          <t>MTSN 1 OKUT (424967)</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4746,15 +4536,10 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>BPN OKU (431142)</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
-        <is>
-          <t>BPN OKU (431142)</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4846,15 +4631,10 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUS (440502)</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUS (440502)</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4946,15 +4726,10 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>MTSN 1 OKU (426050)</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
-        <is>
-          <t>MTSN 1 OKU (426050)</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5046,15 +4821,10 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>RUPBASAN BATURAJA</t>
+          <t>RUPBASAN BATURAJA (692725)</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
-        <is>
-          <t>RUPBASAN BATURAJA (692725)</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5146,15 +4916,10 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>MAN 2 OKUS (597558)</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
-        <is>
-          <t>MAN 2 OKUS (597558)</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5246,15 +5011,10 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>MAN 1 OKUS (662127)</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
-        <is>
-          <t>MAN 1 OKUS (662127)</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5346,15 +5106,10 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>MAN 1 OKUT (426066)</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
-        <is>
-          <t>MAN 1 OKUT (426066)</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5446,15 +5201,10 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKU (418459)</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
-        <is>
-          <t>KEMENAG OKU (418459)</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5546,15 +5296,10 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>MTSN 1 OKUS (553792)</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
-        <is>
-          <t>MTSN 1 OKUS (553792)</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5646,15 +5391,10 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUT (666503)</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUT (666503)</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5746,15 +5486,10 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>KEJARI  OKUS</t>
+          <t>KEJARI  OKUS ('007208)</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
-        <is>
-          <t>KEJARI  OKUS ('007208)</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5846,15 +5581,10 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKU (418458)</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
-        <is>
-          <t>KEMENAG OKU (418458)</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5946,15 +5676,10 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>RUMKIT NOESMIR (344894)</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
-        <is>
-          <t>RUMKIT NOESMIR (344894)</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6046,15 +5771,10 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>BNN OKUT (111079)</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
-        <is>
-          <t>BNN OKUT (111079)</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6146,15 +5866,10 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>LOKA LABKESMAS (690801)</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
-        <is>
-          <t>LOKA LABKESMAS (690801)</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6246,15 +5961,10 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUT (666501)</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUT (666501)</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6346,15 +6056,10 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>BAWASLU OKU (419006)</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
-        <is>
-          <t>BAWASLU OKU (419006)</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6446,15 +6151,10 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>BAWASLU OKUS (686503)</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
-        <is>
-          <t>BAWASLU OKUS (686503)</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6546,15 +6246,10 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>PA  MUARADUA (403410)</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
-        <is>
-          <t>PA  MUARADUA (403410)</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6646,15 +6341,10 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>MTSN 3 OKUS (574370)</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
-        <is>
-          <t>MTSN 3 OKUS (574370)</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6746,15 +6436,10 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUT (666507)</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUT (666507)</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6846,15 +6531,10 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>PN BATURAJA ('099228)</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
-        <is>
-          <t>PN BATURAJA ('099228)</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6946,15 +6626,10 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKU (418457)</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
-        <is>
-          <t>KEMENAG OKU (418457)</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -7046,15 +6721,10 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUT (666502)</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUT (666502)</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -7146,15 +6816,10 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>MAN 1 OKU (424245)</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
-        <is>
-          <t>MAN 1 OKU (424245)</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -7246,15 +6911,10 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKU (418461)</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
-        <is>
-          <t>KEMENAG OKU (418461)</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -7346,15 +7006,10 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>DISNAKERTRANS OKUT</t>
+          <t>DISNAKERTRANS OKUT (691653)</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
-        <is>
-          <t>DISNAKERTRANS OKUT (691653)</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
